--- a/inst/extdata/fort_peck_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/fort_peck_tribe_criteria_crosswalk.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/k_salkgundersen_tetratech_com/Documents/EPA/R8_AssessmentTool/5_Work/Crosswalks/individual_criteria_crosswalks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD7FB050-DD07-47CF-9963-5BDED1BFAA5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8812648A-A7E5-40A8-8E4A-550808961698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A9D2C00B-42FB-4D75-83D9-FF6DA97293BD}"/>
+    <workbookView xWindow="28690" yWindow="-110" windowWidth="20710" windowHeight="11020" xr2:uid="{A9D2C00B-42FB-4D75-83D9-FF6DA97293BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AQ$50</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="133">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -472,12 +475,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -492,7 +501,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -507,6 +516,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -843,10 +855,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48473D4D-2A67-413E-80AF-8677973F00EA}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AQ50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.08984375" customWidth="1"/>
+    <col min="18" max="18" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="4" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" s="4" customFormat="1" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -977,7 +998,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5"/>
       <c r="B2" s="5" t="s">
         <v>43</v>
@@ -1046,7 +1067,7 @@
       <c r="AL2" s="5"/>
       <c r="AM2" s="5"/>
     </row>
-    <row r="3" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5"/>
       <c r="B3" s="5" t="s">
         <v>43</v>
@@ -1115,7 +1136,7 @@
       <c r="AL3" s="5"/>
       <c r="AM3" s="5"/>
     </row>
-    <row r="4" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5"/>
       <c r="B4" s="5" t="s">
         <v>43</v>
@@ -1182,7 +1203,7 @@
       <c r="AL4" s="5"/>
       <c r="AM4" s="5"/>
     </row>
-    <row r="5" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5"/>
       <c r="B5" s="5" t="s">
         <v>43</v>
@@ -1249,7 +1270,7 @@
       <c r="AL5" s="5"/>
       <c r="AM5" s="5"/>
     </row>
-    <row r="6" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5"/>
       <c r="B6" s="5" t="s">
         <v>43</v>
@@ -1316,7 +1337,7 @@
       <c r="AL6" s="5"/>
       <c r="AM6" s="5"/>
     </row>
-    <row r="7" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5"/>
       <c r="B7" s="5" t="s">
         <v>43</v>
@@ -1383,7 +1404,7 @@
       <c r="AL7" s="5"/>
       <c r="AM7" s="5"/>
     </row>
-    <row r="8" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5"/>
       <c r="B8" s="5" t="s">
         <v>43</v>
@@ -1450,7 +1471,7 @@
       <c r="AL8" s="5"/>
       <c r="AM8" s="5"/>
     </row>
-    <row r="9" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5"/>
       <c r="B9" s="5" t="s">
         <v>43</v>
@@ -1517,7 +1538,7 @@
       <c r="AL9" s="5"/>
       <c r="AM9" s="5"/>
     </row>
-    <row r="10" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5"/>
       <c r="B10" s="5" t="s">
         <v>43</v>
@@ -1584,7 +1605,7 @@
       <c r="AL10" s="5"/>
       <c r="AM10" s="5"/>
     </row>
-    <row r="11" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5"/>
       <c r="B11" s="5" t="s">
         <v>43</v>
@@ -1651,7 +1672,7 @@
       <c r="AL11" s="5"/>
       <c r="AM11" s="5"/>
     </row>
-    <row r="12" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5"/>
       <c r="B12" s="5" t="s">
         <v>43</v>
@@ -1716,7 +1737,7 @@
       <c r="AL12" s="5"/>
       <c r="AM12" s="5"/>
     </row>
-    <row r="13" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5"/>
       <c r="B13" s="5" t="s">
         <v>43</v>
@@ -1781,7 +1802,7 @@
       <c r="AL13" s="5"/>
       <c r="AM13" s="5"/>
     </row>
-    <row r="14" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5"/>
       <c r="B14" s="5" t="s">
         <v>43</v>
@@ -1846,7 +1867,7 @@
       <c r="AL14" s="5"/>
       <c r="AM14" s="5"/>
     </row>
-    <row r="15" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5"/>
       <c r="B15" s="5" t="s">
         <v>43</v>
@@ -1911,7 +1932,7 @@
       <c r="AL15" s="5"/>
       <c r="AM15" s="5"/>
     </row>
-    <row r="16" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5"/>
       <c r="B16" s="5" t="s">
         <v>43</v>
@@ -1976,7 +1997,7 @@
       <c r="AL16" s="5"/>
       <c r="AM16" s="5"/>
     </row>
-    <row r="17" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5"/>
       <c r="B17" s="5" t="s">
         <v>43</v>
@@ -2041,7 +2062,7 @@
       <c r="AL17" s="5"/>
       <c r="AM17" s="5"/>
     </row>
-    <row r="18" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="5"/>
       <c r="B18" s="5" t="s">
         <v>43</v>
@@ -2106,7 +2127,7 @@
       <c r="AL18" s="5"/>
       <c r="AM18" s="5"/>
     </row>
-    <row r="19" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="5"/>
       <c r="B19" s="5" t="s">
         <v>43</v>
@@ -2171,7 +2192,7 @@
       <c r="AL19" s="5"/>
       <c r="AM19" s="5"/>
     </row>
-    <row r="20" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5"/>
       <c r="B20" s="5" t="s">
         <v>43</v>
@@ -2236,7 +2257,7 @@
       <c r="AL20" s="5"/>
       <c r="AM20" s="5"/>
     </row>
-    <row r="21" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5"/>
       <c r="B21" s="5" t="s">
         <v>43</v>
@@ -2301,7 +2322,7 @@
       <c r="AL21" s="5"/>
       <c r="AM21" s="5"/>
     </row>
-    <row r="22" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="5"/>
       <c r="B22" s="5" t="s">
         <v>43</v>
@@ -2366,7 +2387,7 @@
       <c r="AL22" s="5"/>
       <c r="AM22" s="5"/>
     </row>
-    <row r="23" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5"/>
       <c r="B23" s="5" t="s">
         <v>43</v>
@@ -2431,7 +2452,7 @@
       <c r="AL23" s="5"/>
       <c r="AM23" s="5"/>
     </row>
-    <row r="24" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5"/>
       <c r="B24" s="5" t="s">
         <v>43</v>
@@ -2498,7 +2519,7 @@
       <c r="AL24" s="5"/>
       <c r="AM24" s="5"/>
     </row>
-    <row r="25" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="5"/>
       <c r="B25" s="5" t="s">
         <v>43</v>
@@ -2554,8 +2575,12 @@
       <c r="Y25" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="Z25" s="5"/>
-      <c r="AA25" s="5"/>
+      <c r="Z25" s="6">
+        <v>45809</v>
+      </c>
+      <c r="AA25" s="6">
+        <v>45930</v>
+      </c>
       <c r="AB25" s="5"/>
       <c r="AC25" s="5"/>
       <c r="AD25" s="5"/>
@@ -2569,7 +2594,7 @@
       <c r="AL25" s="5"/>
       <c r="AM25" s="5"/>
     </row>
-    <row r="26" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="5"/>
       <c r="B26" s="5" t="s">
         <v>43</v>
@@ -2625,8 +2650,12 @@
       <c r="Y26" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="Z26" s="5"/>
-      <c r="AA26" s="5"/>
+      <c r="Z26" s="6">
+        <v>45809</v>
+      </c>
+      <c r="AA26" s="6">
+        <v>45930</v>
+      </c>
       <c r="AB26" s="5"/>
       <c r="AC26" s="5"/>
       <c r="AD26" s="5"/>
@@ -2640,7 +2669,7 @@
       <c r="AL26" s="5"/>
       <c r="AM26" s="5"/>
     </row>
-    <row r="27" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="5"/>
       <c r="B27" s="5" t="s">
         <v>43</v>
@@ -2694,8 +2723,12 @@
       <c r="Y27" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="Z27" s="5"/>
-      <c r="AA27" s="5"/>
+      <c r="Z27" s="6">
+        <v>45809</v>
+      </c>
+      <c r="AA27" s="6">
+        <v>45930</v>
+      </c>
       <c r="AB27" s="5"/>
       <c r="AC27" s="5"/>
       <c r="AD27" s="5"/>
@@ -2709,7 +2742,7 @@
       <c r="AL27" s="5"/>
       <c r="AM27" s="5"/>
     </row>
-    <row r="28" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="5"/>
       <c r="B28" s="5" t="s">
         <v>43</v>
@@ -2763,8 +2796,12 @@
       <c r="Y28" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="Z28" s="5"/>
-      <c r="AA28" s="5"/>
+      <c r="Z28" s="6">
+        <v>45809</v>
+      </c>
+      <c r="AA28" s="6">
+        <v>45930</v>
+      </c>
       <c r="AB28" s="5"/>
       <c r="AC28" s="5"/>
       <c r="AD28" s="5"/>
@@ -2778,7 +2815,7 @@
       <c r="AL28" s="5"/>
       <c r="AM28" s="5"/>
     </row>
-    <row r="29" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="5"/>
       <c r="B29" s="5" t="s">
         <v>43</v>
@@ -2829,9 +2866,15 @@
       <c r="V29" s="5"/>
       <c r="W29" s="5"/>
       <c r="X29" s="5"/>
-      <c r="Y29" s="5"/>
-      <c r="Z29" s="5"/>
-      <c r="AA29" s="5"/>
+      <c r="Y29" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z29" s="6">
+        <v>45809</v>
+      </c>
+      <c r="AA29" s="6">
+        <v>45930</v>
+      </c>
       <c r="AB29" s="5"/>
       <c r="AC29" s="5"/>
       <c r="AD29" s="5"/>
@@ -2845,7 +2888,7 @@
       <c r="AL29" s="5"/>
       <c r="AM29" s="5"/>
     </row>
-    <row r="30" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5"/>
       <c r="B30" s="5" t="s">
         <v>43</v>
@@ -2916,7 +2959,7 @@
       <c r="AL30" s="5"/>
       <c r="AM30" s="5"/>
     </row>
-    <row r="31" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5"/>
       <c r="B31" s="5" t="s">
         <v>43</v>
@@ -2987,7 +3030,7 @@
       <c r="AL31" s="5"/>
       <c r="AM31" s="5"/>
     </row>
-    <row r="32" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5"/>
       <c r="B32" s="5" t="s">
         <v>43</v>
@@ -3058,7 +3101,7 @@
       <c r="AL32" s="5"/>
       <c r="AM32" s="5"/>
     </row>
-    <row r="33" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="5"/>
       <c r="B33" s="5" t="s">
         <v>43</v>
@@ -3129,7 +3172,7 @@
       <c r="AL33" s="5"/>
       <c r="AM33" s="5"/>
     </row>
-    <row r="34" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="5"/>
       <c r="B34" s="5" t="s">
         <v>43</v>
@@ -3200,7 +3243,7 @@
       <c r="AL34" s="5"/>
       <c r="AM34" s="5"/>
     </row>
-    <row r="35" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="5"/>
       <c r="B35" s="5" t="s">
         <v>43</v>
@@ -3271,7 +3314,7 @@
       <c r="AL35" s="5"/>
       <c r="AM35" s="5"/>
     </row>
-    <row r="36" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="5"/>
       <c r="B36" s="5" t="s">
         <v>43</v>
@@ -3342,7 +3385,7 @@
       <c r="AL36" s="5"/>
       <c r="AM36" s="5"/>
     </row>
-    <row r="37" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="5"/>
       <c r="B37" s="5" t="s">
         <v>43</v>
@@ -3413,7 +3456,7 @@
       <c r="AL37" s="5"/>
       <c r="AM37" s="5"/>
     </row>
-    <row r="38" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="5"/>
       <c r="B38" s="5" t="s">
         <v>43</v>
@@ -3484,7 +3527,7 @@
       <c r="AL38" s="5"/>
       <c r="AM38" s="5"/>
     </row>
-    <row r="39" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="5"/>
       <c r="B39" s="5" t="s">
         <v>43</v>
@@ -3555,7 +3598,7 @@
       <c r="AL39" s="5"/>
       <c r="AM39" s="5"/>
     </row>
-    <row r="40" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="5"/>
       <c r="B40" s="5" t="s">
         <v>43</v>
@@ -3636,7 +3679,7 @@
       </c>
       <c r="AM40" s="5"/>
     </row>
-    <row r="41" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="5"/>
       <c r="B41" s="5" t="s">
         <v>43</v>
@@ -3717,7 +3760,7 @@
       </c>
       <c r="AM41" s="5"/>
     </row>
-    <row r="42" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="5"/>
       <c r="B42" s="5" t="s">
         <v>43</v>
@@ -3798,7 +3841,7 @@
       </c>
       <c r="AM42" s="5"/>
     </row>
-    <row r="43" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5"/>
       <c r="B43" s="5" t="s">
         <v>43</v>
@@ -3879,7 +3922,7 @@
       </c>
       <c r="AM43" s="5"/>
     </row>
-    <row r="44" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5"/>
       <c r="B44" s="5" t="s">
         <v>43</v>
@@ -3960,7 +4003,7 @@
       </c>
       <c r="AM44" s="5"/>
     </row>
-    <row r="45" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="5"/>
       <c r="B45" s="5" t="s">
         <v>43</v>
@@ -4041,7 +4084,7 @@
       </c>
       <c r="AM45" s="5"/>
     </row>
-    <row r="46" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="5"/>
       <c r="B46" s="5" t="s">
         <v>43</v>
@@ -4122,7 +4165,7 @@
       </c>
       <c r="AM46" s="5"/>
     </row>
-    <row r="47" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="5"/>
       <c r="B47" s="5" t="s">
         <v>43</v>
@@ -4203,7 +4246,7 @@
       </c>
       <c r="AM47" s="5"/>
     </row>
-    <row r="48" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="5"/>
       <c r="B48" s="5" t="s">
         <v>43</v>
@@ -4284,7 +4327,7 @@
       </c>
       <c r="AM48" s="5"/>
     </row>
-    <row r="49" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="5"/>
       <c r="B49" s="5" t="s">
         <v>43</v>
@@ -4365,7 +4408,7 @@
       </c>
       <c r="AM49" s="5"/>
     </row>
-    <row r="50" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="5"/>
       <c r="B50" s="5" t="s">
         <v>43</v>
@@ -4447,6 +4490,13 @@
       <c r="AM50" s="5"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AQ50" xr:uid="{48473D4D-2A67-413E-80AF-8677973F00EA}">
+    <filterColumn colId="17">
+      <filters>
+        <filter val="n-season"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/inst/extdata/fort_peck_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/fort_peck_tribe_criteria_crosswalk.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8812648A-A7E5-40A8-8E4A-550808961698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{326FB558-93B4-47D8-B227-45D3F1BFE90B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28690" yWindow="-110" windowWidth="20710" windowHeight="11020" xr2:uid="{A9D2C00B-42FB-4D75-83D9-FF6DA97293BD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A9D2C00B-42FB-4D75-83D9-FF6DA97293BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="131">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -242,9 +242,6 @@
     <t>MG/L</t>
   </si>
   <si>
-    <t>Ammonia Nitrogen</t>
-  </si>
-  <si>
     <t>AMMONIA-NITROGEN</t>
   </si>
   <si>
@@ -302,9 +299,6 @@
     <t>COPPER</t>
   </si>
   <si>
-    <t>Floride</t>
-  </si>
-  <si>
     <t>FLUORIDE</t>
   </si>
   <si>
@@ -335,9 +329,6 @@
     <t>NumberNotMeeting</t>
   </si>
   <si>
-    <t>E. coli</t>
-  </si>
-  <si>
     <t>Primary Recreation</t>
   </si>
   <si>
@@ -359,9 +350,6 @@
     <t>Secondary Recreation</t>
   </si>
   <si>
-    <t>Oxygen</t>
-  </si>
-  <si>
     <t>DISSOLVED OXYGEN (DO)</t>
   </si>
   <si>
@@ -404,9 +392,6 @@
     <t>e^(0.7977*ln(hardness)-3.909)</t>
   </si>
   <si>
-    <t>Chromium (III)</t>
-  </si>
-  <si>
     <t>CHROMIUM(III)</t>
   </si>
   <si>
@@ -438,6 +423,15 @@
   </si>
   <si>
     <t>e^(0.8473*ln(hardness)+0.884)</t>
+  </si>
+  <si>
+    <t>ESCHERICHIA COLI (E. COLI)</t>
+  </si>
+  <si>
+    <t>DISSOLVED OXYGEN</t>
+  </si>
+  <si>
+    <t>CHROMIUM, TRIVALENT, TOTAL</t>
   </si>
 </sst>
 </file>
@@ -855,7 +849,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48473D4D-2A67-413E-80AF-8677973F00EA}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AQ50"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -998,7 +991,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="5"/>
       <c r="B2" s="5" t="s">
         <v>43</v>
@@ -1067,7 +1060,7 @@
       <c r="AL2" s="5"/>
       <c r="AM2" s="5"/>
     </row>
-    <row r="3" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="5"/>
       <c r="B3" s="5" t="s">
         <v>43</v>
@@ -1136,7 +1129,7 @@
       <c r="AL3" s="5"/>
       <c r="AM3" s="5"/>
     </row>
-    <row r="4" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="5"/>
       <c r="B4" s="5" t="s">
         <v>43</v>
@@ -1203,7 +1196,7 @@
       <c r="AL4" s="5"/>
       <c r="AM4" s="5"/>
     </row>
-    <row r="5" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="5"/>
       <c r="B5" s="5" t="s">
         <v>43</v>
@@ -1270,7 +1263,7 @@
       <c r="AL5" s="5"/>
       <c r="AM5" s="5"/>
     </row>
-    <row r="6" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="5"/>
       <c r="B6" s="5" t="s">
         <v>43</v>
@@ -1337,7 +1330,7 @@
       <c r="AL6" s="5"/>
       <c r="AM6" s="5"/>
     </row>
-    <row r="7" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="5"/>
       <c r="B7" s="5" t="s">
         <v>43</v>
@@ -1404,7 +1397,7 @@
       <c r="AL7" s="5"/>
       <c r="AM7" s="5"/>
     </row>
-    <row r="8" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="5"/>
       <c r="B8" s="5" t="s">
         <v>43</v>
@@ -1471,7 +1464,7 @@
       <c r="AL8" s="5"/>
       <c r="AM8" s="5"/>
     </row>
-    <row r="9" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="5"/>
       <c r="B9" s="5" t="s">
         <v>43</v>
@@ -1483,7 +1476,7 @@
         <v>45</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
@@ -1527,7 +1520,7 @@
       <c r="AC9" s="5"/>
       <c r="AD9" s="5"/>
       <c r="AE9" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AF9" s="5"/>
       <c r="AG9" s="5"/>
@@ -1538,19 +1531,19 @@
       <c r="AL9" s="5"/>
       <c r="AM9" s="5"/>
     </row>
-    <row r="10" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="5"/>
       <c r="B10" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
@@ -1605,19 +1598,19 @@
       <c r="AL10" s="5"/>
       <c r="AM10" s="5"/>
     </row>
-    <row r="11" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="5"/>
       <c r="B11" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
@@ -1672,19 +1665,19 @@
       <c r="AL11" s="5"/>
       <c r="AM11" s="5"/>
     </row>
-    <row r="12" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="5"/>
       <c r="B12" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
@@ -1737,19 +1730,19 @@
       <c r="AL12" s="5"/>
       <c r="AM12" s="5"/>
     </row>
-    <row r="13" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="5"/>
       <c r="B13" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
@@ -1802,19 +1795,19 @@
       <c r="AL13" s="5"/>
       <c r="AM13" s="5"/>
     </row>
-    <row r="14" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="5"/>
       <c r="B14" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
@@ -1867,19 +1860,19 @@
       <c r="AL14" s="5"/>
       <c r="AM14" s="5"/>
     </row>
-    <row r="15" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="5"/>
       <c r="B15" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C15" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="E15" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>80</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
@@ -1932,19 +1925,19 @@
       <c r="AL15" s="5"/>
       <c r="AM15" s="5"/>
     </row>
-    <row r="16" spans="1:43" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="5"/>
       <c r="B16" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>82</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -1997,19 +1990,19 @@
       <c r="AL16" s="5"/>
       <c r="AM16" s="5"/>
     </row>
-    <row r="17" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="5"/>
       <c r="B17" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C17" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>84</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -2062,19 +2055,19 @@
       <c r="AL17" s="5"/>
       <c r="AM17" s="5"/>
     </row>
-    <row r="18" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="5"/>
       <c r="B18" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C18" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>86</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
@@ -2127,19 +2120,19 @@
       <c r="AL18" s="5"/>
       <c r="AM18" s="5"/>
     </row>
-    <row r="19" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="5"/>
       <c r="B19" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
@@ -2192,19 +2185,19 @@
       <c r="AL19" s="5"/>
       <c r="AM19" s="5"/>
     </row>
-    <row r="20" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="5"/>
       <c r="B20" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C20" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>76</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>77</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -2257,19 +2250,19 @@
       <c r="AL20" s="5"/>
       <c r="AM20" s="5"/>
     </row>
-    <row r="21" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="5"/>
       <c r="B21" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
@@ -2322,19 +2315,19 @@
       <c r="AL21" s="5"/>
       <c r="AM21" s="5"/>
     </row>
-    <row r="22" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="5"/>
       <c r="B22" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
@@ -2387,19 +2380,19 @@
       <c r="AL22" s="5"/>
       <c r="AM22" s="5"/>
     </row>
-    <row r="23" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="5"/>
       <c r="B23" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
@@ -2452,19 +2445,19 @@
       <c r="AL23" s="5"/>
       <c r="AM23" s="5"/>
     </row>
-    <row r="24" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="5"/>
       <c r="B24" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
@@ -2498,7 +2491,7 @@
         <v>1</v>
       </c>
       <c r="U24" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="V24" s="5"/>
       <c r="W24" s="5"/>
@@ -2525,13 +2518,13 @@
         <v>43</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
@@ -2552,28 +2545,28 @@
       </c>
       <c r="O25" s="5"/>
       <c r="P25" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q25" s="5">
         <v>1</v>
       </c>
       <c r="R25" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="S25" s="5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="T25" s="5">
         <v>1</v>
       </c>
       <c r="U25" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="V25" s="5"/>
       <c r="W25" s="5"/>
       <c r="X25" s="5"/>
       <c r="Y25" s="5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="Z25" s="6">
         <v>45809</v>
@@ -2600,13 +2593,13 @@
         <v>43</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
@@ -2627,28 +2620,28 @@
       </c>
       <c r="O26" s="5"/>
       <c r="P26" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q26" s="5">
         <v>1</v>
       </c>
       <c r="R26" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="S26" s="5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="T26" s="5">
         <v>1</v>
       </c>
       <c r="U26" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="V26" s="5"/>
       <c r="W26" s="5"/>
       <c r="X26" s="5"/>
       <c r="Y26" s="5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="Z26" s="6">
         <v>45809</v>
@@ -2675,13 +2668,13 @@
         <v>43</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
@@ -2700,28 +2693,28 @@
       </c>
       <c r="O27" s="5"/>
       <c r="P27" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q27" s="5">
         <v>1</v>
       </c>
       <c r="R27" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="S27" s="5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="T27" s="5">
         <v>1</v>
       </c>
       <c r="U27" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="V27" s="5"/>
       <c r="W27" s="5"/>
       <c r="X27" s="5"/>
       <c r="Y27" s="5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="Z27" s="6">
         <v>45809</v>
@@ -2748,13 +2741,13 @@
         <v>43</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -2773,28 +2766,28 @@
       </c>
       <c r="O28" s="5"/>
       <c r="P28" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q28" s="5">
         <v>1</v>
       </c>
       <c r="R28" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="S28" s="5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="T28" s="5">
         <v>1</v>
       </c>
       <c r="U28" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="V28" s="5"/>
       <c r="W28" s="5"/>
       <c r="X28" s="5"/>
       <c r="Y28" s="5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="Z28" s="6">
         <v>45809</v>
@@ -2821,13 +2814,13 @@
         <v>43</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -2846,28 +2839,28 @@
       </c>
       <c r="O29" s="5"/>
       <c r="P29" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q29" s="5">
         <v>1</v>
       </c>
       <c r="R29" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="S29" s="5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="T29" s="5">
         <v>1</v>
       </c>
       <c r="U29" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="V29" s="5"/>
       <c r="W29" s="5"/>
       <c r="X29" s="5"/>
       <c r="Y29" s="5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="Z29" s="6">
         <v>45809</v>
@@ -2888,22 +2881,22 @@
       <c r="AL29" s="5"/>
       <c r="AM29" s="5"/>
     </row>
-    <row r="30" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="5"/>
       <c r="B30" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
@@ -2913,7 +2906,7 @@
       </c>
       <c r="K30" s="5"/>
       <c r="L30" s="5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="M30" s="5" t="s">
         <v>49</v>
@@ -2932,13 +2925,13 @@
         <v>51</v>
       </c>
       <c r="S30" s="5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="T30" s="5">
         <v>1</v>
       </c>
       <c r="U30" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="V30" s="5"/>
       <c r="W30" s="5"/>
@@ -2959,22 +2952,22 @@
       <c r="AL30" s="5"/>
       <c r="AM30" s="5"/>
     </row>
-    <row r="31" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="5"/>
       <c r="B31" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
@@ -2984,7 +2977,7 @@
       </c>
       <c r="K31" s="5"/>
       <c r="L31" s="5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="M31" s="5" t="s">
         <v>49</v>
@@ -3003,13 +2996,13 @@
         <v>51</v>
       </c>
       <c r="S31" s="5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="T31" s="5">
         <v>1</v>
       </c>
       <c r="U31" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="V31" s="5"/>
       <c r="W31" s="5"/>
@@ -3030,22 +3023,22 @@
       <c r="AL31" s="5"/>
       <c r="AM31" s="5"/>
     </row>
-    <row r="32" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="5"/>
       <c r="B32" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
@@ -3055,7 +3048,7 @@
       </c>
       <c r="K32" s="5"/>
       <c r="L32" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="M32" s="5" t="s">
         <v>49</v>
@@ -3074,13 +3067,13 @@
         <v>51</v>
       </c>
       <c r="S32" s="5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="T32" s="5">
         <v>1</v>
       </c>
       <c r="U32" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="V32" s="5"/>
       <c r="W32" s="5"/>
@@ -3101,22 +3094,22 @@
       <c r="AL32" s="5"/>
       <c r="AM32" s="5"/>
     </row>
-    <row r="33" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="5"/>
       <c r="B33" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
@@ -3126,7 +3119,7 @@
       </c>
       <c r="K33" s="5"/>
       <c r="L33" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="M33" s="5" t="s">
         <v>49</v>
@@ -3145,13 +3138,13 @@
         <v>51</v>
       </c>
       <c r="S33" s="5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="T33" s="5">
         <v>1</v>
       </c>
       <c r="U33" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="V33" s="5"/>
       <c r="W33" s="5"/>
@@ -3172,22 +3165,22 @@
       <c r="AL33" s="5"/>
       <c r="AM33" s="5"/>
     </row>
-    <row r="34" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="5"/>
       <c r="B34" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
@@ -3197,7 +3190,7 @@
       </c>
       <c r="K34" s="5"/>
       <c r="L34" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="M34" s="5" t="s">
         <v>49</v>
@@ -3216,13 +3209,13 @@
         <v>51</v>
       </c>
       <c r="S34" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="T34" s="5">
         <v>1</v>
       </c>
       <c r="U34" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="V34" s="5"/>
       <c r="W34" s="5"/>
@@ -3243,22 +3236,22 @@
       <c r="AL34" s="5"/>
       <c r="AM34" s="5"/>
     </row>
-    <row r="35" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="5"/>
       <c r="B35" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
@@ -3268,7 +3261,7 @@
       </c>
       <c r="K35" s="5"/>
       <c r="L35" s="5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="M35" s="5" t="s">
         <v>49</v>
@@ -3287,13 +3280,13 @@
         <v>51</v>
       </c>
       <c r="S35" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="T35" s="5">
         <v>1</v>
       </c>
       <c r="U35" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="V35" s="5"/>
       <c r="W35" s="5"/>
@@ -3314,22 +3307,22 @@
       <c r="AL35" s="5"/>
       <c r="AM35" s="5"/>
     </row>
-    <row r="36" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="5"/>
       <c r="B36" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
@@ -3339,7 +3332,7 @@
       </c>
       <c r="K36" s="5"/>
       <c r="L36" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="M36" s="5" t="s">
         <v>49</v>
@@ -3358,13 +3351,13 @@
         <v>51</v>
       </c>
       <c r="S36" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="T36" s="5">
         <v>1</v>
       </c>
       <c r="U36" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="V36" s="5"/>
       <c r="W36" s="5"/>
@@ -3385,22 +3378,22 @@
       <c r="AL36" s="5"/>
       <c r="AM36" s="5"/>
     </row>
-    <row r="37" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="5"/>
       <c r="B37" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
@@ -3410,7 +3403,7 @@
       </c>
       <c r="K37" s="5"/>
       <c r="L37" s="5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="M37" s="5" t="s">
         <v>49</v>
@@ -3429,13 +3422,13 @@
         <v>51</v>
       </c>
       <c r="S37" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="T37" s="5">
         <v>1</v>
       </c>
       <c r="U37" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="V37" s="5"/>
       <c r="W37" s="5"/>
@@ -3456,22 +3449,22 @@
       <c r="AL37" s="5"/>
       <c r="AM37" s="5"/>
     </row>
-    <row r="38" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="5"/>
       <c r="B38" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
@@ -3481,7 +3474,7 @@
       </c>
       <c r="K38" s="5"/>
       <c r="L38" s="5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="M38" s="5" t="s">
         <v>49</v>
@@ -3500,13 +3493,13 @@
         <v>51</v>
       </c>
       <c r="S38" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="T38" s="5">
         <v>1</v>
       </c>
       <c r="U38" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="V38" s="5"/>
       <c r="W38" s="5"/>
@@ -3527,22 +3520,22 @@
       <c r="AL38" s="5"/>
       <c r="AM38" s="5"/>
     </row>
-    <row r="39" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="5"/>
       <c r="B39" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
@@ -3552,7 +3545,7 @@
       </c>
       <c r="K39" s="5"/>
       <c r="L39" s="5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="M39" s="5" t="s">
         <v>49</v>
@@ -3571,13 +3564,13 @@
         <v>51</v>
       </c>
       <c r="S39" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="T39" s="5">
         <v>1</v>
       </c>
       <c r="U39" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="V39" s="5"/>
       <c r="W39" s="5"/>
@@ -3598,22 +3591,22 @@
       <c r="AL39" s="5"/>
       <c r="AM39" s="5"/>
     </row>
-    <row r="40" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="5"/>
       <c r="B40" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5" t="s">
@@ -3626,7 +3619,7 @@
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
       <c r="M40" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="N40" s="5"/>
       <c r="O40" s="5"/>
@@ -3646,7 +3639,7 @@
         <v>1</v>
       </c>
       <c r="U40" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="V40" s="5"/>
       <c r="W40" s="5"/>
@@ -3658,13 +3651,13 @@
       <c r="AC40" s="5"/>
       <c r="AD40" s="5"/>
       <c r="AE40" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AF40" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG40" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AH40" s="5"/>
       <c r="AI40" s="5"/>
@@ -3679,22 +3672,22 @@
       </c>
       <c r="AM40" s="5"/>
     </row>
-    <row r="41" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="5"/>
       <c r="B41" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="5" t="s">
@@ -3707,7 +3700,7 @@
       <c r="K41" s="5"/>
       <c r="L41" s="5"/>
       <c r="M41" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="N41" s="5"/>
       <c r="O41" s="5"/>
@@ -3721,13 +3714,13 @@
         <v>51</v>
       </c>
       <c r="S41" s="5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="T41" s="5">
         <v>1</v>
       </c>
       <c r="U41" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="V41" s="5"/>
       <c r="W41" s="5"/>
@@ -3739,13 +3732,13 @@
       <c r="AC41" s="5"/>
       <c r="AD41" s="5"/>
       <c r="AE41" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="AF41" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG41" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="AH41" s="5"/>
       <c r="AI41" s="5"/>
@@ -3760,22 +3753,22 @@
       </c>
       <c r="AM41" s="5"/>
     </row>
-    <row r="42" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="5"/>
       <c r="B42" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5" t="s">
@@ -3788,7 +3781,7 @@
       <c r="K42" s="5"/>
       <c r="L42" s="5"/>
       <c r="M42" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="N42" s="5"/>
       <c r="O42" s="5"/>
@@ -3808,7 +3801,7 @@
         <v>1</v>
       </c>
       <c r="U42" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="V42" s="5"/>
       <c r="W42" s="5"/>
@@ -3820,13 +3813,13 @@
       <c r="AC42" s="5"/>
       <c r="AD42" s="5"/>
       <c r="AE42" s="5" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="AF42" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG42" s="5" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="AH42" s="5"/>
       <c r="AI42" s="5"/>
@@ -3841,22 +3834,22 @@
       </c>
       <c r="AM42" s="5"/>
     </row>
-    <row r="43" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="5"/>
       <c r="B43" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5" t="s">
@@ -3869,7 +3862,7 @@
       <c r="K43" s="5"/>
       <c r="L43" s="5"/>
       <c r="M43" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="N43" s="5"/>
       <c r="O43" s="5"/>
@@ -3883,13 +3876,13 @@
         <v>51</v>
       </c>
       <c r="S43" s="5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="T43" s="5">
         <v>1</v>
       </c>
       <c r="U43" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="V43" s="5"/>
       <c r="W43" s="5"/>
@@ -3901,13 +3894,13 @@
       <c r="AC43" s="5"/>
       <c r="AD43" s="5"/>
       <c r="AE43" s="5" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="AF43" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="AG43" s="5" t="s">
         <v>119</v>
-      </c>
-      <c r="AG43" s="5" t="s">
-        <v>124</v>
       </c>
       <c r="AH43" s="5"/>
       <c r="AI43" s="5"/>
@@ -3922,22 +3915,22 @@
       </c>
       <c r="AM43" s="5"/>
     </row>
-    <row r="44" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="5"/>
       <c r="B44" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5" t="s">
@@ -3950,7 +3943,7 @@
       <c r="K44" s="5"/>
       <c r="L44" s="5"/>
       <c r="M44" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="N44" s="5"/>
       <c r="O44" s="5"/>
@@ -3970,7 +3963,7 @@
         <v>1</v>
       </c>
       <c r="U44" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="V44" s="5"/>
       <c r="W44" s="5"/>
@@ -3982,13 +3975,13 @@
       <c r="AC44" s="5"/>
       <c r="AD44" s="5"/>
       <c r="AE44" s="5" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="AF44" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG44" s="5" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="AH44" s="5"/>
       <c r="AI44" s="5"/>
@@ -4003,22 +3996,22 @@
       </c>
       <c r="AM44" s="5"/>
     </row>
-    <row r="45" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="5"/>
       <c r="B45" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5" t="s">
@@ -4031,7 +4024,7 @@
       <c r="K45" s="5"/>
       <c r="L45" s="5"/>
       <c r="M45" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="N45" s="5"/>
       <c r="O45" s="5"/>
@@ -4045,13 +4038,13 @@
         <v>51</v>
       </c>
       <c r="S45" s="5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="T45" s="5">
         <v>1</v>
       </c>
       <c r="U45" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="V45" s="5"/>
       <c r="W45" s="5"/>
@@ -4063,13 +4056,13 @@
       <c r="AC45" s="5"/>
       <c r="AD45" s="5"/>
       <c r="AE45" s="5" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="AF45" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG45" s="5" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="AH45" s="5"/>
       <c r="AI45" s="5"/>
@@ -4084,22 +4077,22 @@
       </c>
       <c r="AM45" s="5"/>
     </row>
-    <row r="46" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="5"/>
       <c r="B46" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5" t="s">
@@ -4112,7 +4105,7 @@
       <c r="K46" s="5"/>
       <c r="L46" s="5"/>
       <c r="M46" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="N46" s="5"/>
       <c r="O46" s="5"/>
@@ -4132,7 +4125,7 @@
         <v>1</v>
       </c>
       <c r="U46" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="V46" s="5"/>
       <c r="W46" s="5"/>
@@ -4144,13 +4137,13 @@
       <c r="AC46" s="5"/>
       <c r="AD46" s="5"/>
       <c r="AE46" s="5" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="AF46" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG46" s="5" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="AH46" s="5"/>
       <c r="AI46" s="5"/>
@@ -4165,22 +4158,22 @@
       </c>
       <c r="AM46" s="5"/>
     </row>
-    <row r="47" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="5"/>
       <c r="B47" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5" t="s">
@@ -4193,7 +4186,7 @@
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
       <c r="M47" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="N47" s="5"/>
       <c r="O47" s="5"/>
@@ -4207,13 +4200,13 @@
         <v>51</v>
       </c>
       <c r="S47" s="5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="T47" s="5">
         <v>1</v>
       </c>
       <c r="U47" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="V47" s="5"/>
       <c r="W47" s="5"/>
@@ -4225,13 +4218,13 @@
       <c r="AC47" s="5"/>
       <c r="AD47" s="5"/>
       <c r="AE47" s="5" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="AF47" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG47" s="5" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="AH47" s="5"/>
       <c r="AI47" s="5"/>
@@ -4246,22 +4239,22 @@
       </c>
       <c r="AM47" s="5"/>
     </row>
-    <row r="48" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="5"/>
       <c r="B48" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5" t="s">
@@ -4274,7 +4267,7 @@
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
       <c r="M48" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="N48" s="5"/>
       <c r="O48" s="5"/>
@@ -4294,7 +4287,7 @@
         <v>1</v>
       </c>
       <c r="U48" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="V48" s="5"/>
       <c r="W48" s="5"/>
@@ -4306,13 +4299,13 @@
       <c r="AC48" s="5"/>
       <c r="AD48" s="5"/>
       <c r="AE48" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="AF48" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG48" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="AH48" s="5"/>
       <c r="AI48" s="5"/>
@@ -4327,22 +4320,22 @@
       </c>
       <c r="AM48" s="5"/>
     </row>
-    <row r="49" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="5"/>
       <c r="B49" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5" t="s">
@@ -4355,7 +4348,7 @@
       <c r="K49" s="5"/>
       <c r="L49" s="5"/>
       <c r="M49" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="N49" s="5"/>
       <c r="O49" s="5"/>
@@ -4375,7 +4368,7 @@
         <v>1</v>
       </c>
       <c r="U49" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="V49" s="5"/>
       <c r="W49" s="5"/>
@@ -4387,13 +4380,13 @@
       <c r="AC49" s="5"/>
       <c r="AD49" s="5"/>
       <c r="AE49" s="5" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="AF49" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG49" s="5" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="AH49" s="5"/>
       <c r="AI49" s="5"/>
@@ -4408,22 +4401,22 @@
       </c>
       <c r="AM49" s="5"/>
     </row>
-    <row r="50" spans="1:39" s="4" customFormat="1" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="5"/>
       <c r="B50" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5" t="s">
@@ -4436,7 +4429,7 @@
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
       <c r="M50" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="N50" s="5"/>
       <c r="O50" s="5"/>
@@ -4450,13 +4443,13 @@
         <v>51</v>
       </c>
       <c r="S50" s="5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="T50" s="5">
         <v>1</v>
       </c>
       <c r="U50" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="V50" s="5"/>
       <c r="W50" s="5"/>
@@ -4468,13 +4461,13 @@
       <c r="AC50" s="5"/>
       <c r="AD50" s="5"/>
       <c r="AE50" s="5" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="AF50" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG50" s="5" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="AH50" s="5"/>
       <c r="AI50" s="5"/>
@@ -4490,13 +4483,7 @@
       <c r="AM50" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ50" xr:uid="{48473D4D-2A67-413E-80AF-8677973F00EA}">
-    <filterColumn colId="17">
-      <filters>
-        <filter val="n-season"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AQ50" xr:uid="{48473D4D-2A67-413E-80AF-8677973F00EA}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/inst/extdata/fort_peck_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/fort_peck_tribe_criteria_crosswalk.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{326FB558-93B4-47D8-B227-45D3F1BFE90B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7332D495-FC66-4FCE-83BA-16794A495AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A9D2C00B-42FB-4D75-83D9-FF6DA97293BD}"/>
+    <workbookView xWindow="28690" yWindow="-110" windowWidth="20710" windowHeight="11020" xr2:uid="{A9D2C00B-42FB-4D75-83D9-FF6DA97293BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -329,9 +329,6 @@
     <t>NumberNotMeeting</t>
   </si>
   <si>
-    <t>Primary Recreation</t>
-  </si>
-  <si>
     <t>ESCHERICHIA COLI</t>
   </si>
   <si>
@@ -432,6 +429,9 @@
   </si>
   <si>
     <t>CHROMIUM, TRIVALENT, TOTAL</t>
+  </si>
+  <si>
+    <t>Recreation - Primary Contact</t>
   </si>
 </sst>
 </file>
@@ -2518,13 +2518,13 @@
         <v>43</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D25" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
@@ -2545,16 +2545,16 @@
       </c>
       <c r="O25" s="5"/>
       <c r="P25" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q25" s="5">
+        <v>1</v>
+      </c>
+      <c r="R25" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="Q25" s="5">
-        <v>1</v>
-      </c>
-      <c r="R25" s="5" t="s">
+      <c r="S25" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="S25" s="5" t="s">
-        <v>100</v>
       </c>
       <c r="T25" s="5">
         <v>1</v>
@@ -2566,7 +2566,7 @@
       <c r="W25" s="5"/>
       <c r="X25" s="5"/>
       <c r="Y25" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Z25" s="6">
         <v>45809</v>
@@ -2593,13 +2593,13 @@
         <v>43</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
@@ -2620,16 +2620,16 @@
       </c>
       <c r="O26" s="5"/>
       <c r="P26" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q26" s="5">
+        <v>1</v>
+      </c>
+      <c r="R26" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="Q26" s="5">
-        <v>1</v>
-      </c>
-      <c r="R26" s="5" t="s">
+      <c r="S26" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="S26" s="5" t="s">
-        <v>100</v>
       </c>
       <c r="T26" s="5">
         <v>1</v>
@@ -2641,7 +2641,7 @@
       <c r="W26" s="5"/>
       <c r="X26" s="5"/>
       <c r="Y26" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Z26" s="6">
         <v>45809</v>
@@ -2668,13 +2668,13 @@
         <v>43</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D27" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
@@ -2693,16 +2693,16 @@
       </c>
       <c r="O27" s="5"/>
       <c r="P27" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q27" s="5">
+        <v>1</v>
+      </c>
+      <c r="R27" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="Q27" s="5">
-        <v>1</v>
-      </c>
-      <c r="R27" s="5" t="s">
+      <c r="S27" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="S27" s="5" t="s">
-        <v>100</v>
       </c>
       <c r="T27" s="5">
         <v>1</v>
@@ -2714,7 +2714,7 @@
       <c r="W27" s="5"/>
       <c r="X27" s="5"/>
       <c r="Y27" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Z27" s="6">
         <v>45809</v>
@@ -2741,13 +2741,13 @@
         <v>43</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -2766,16 +2766,16 @@
       </c>
       <c r="O28" s="5"/>
       <c r="P28" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q28" s="5">
+        <v>1</v>
+      </c>
+      <c r="R28" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="Q28" s="5">
-        <v>1</v>
-      </c>
-      <c r="R28" s="5" t="s">
+      <c r="S28" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="S28" s="5" t="s">
-        <v>100</v>
       </c>
       <c r="T28" s="5">
         <v>1</v>
@@ -2787,7 +2787,7 @@
       <c r="W28" s="5"/>
       <c r="X28" s="5"/>
       <c r="Y28" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Z28" s="6">
         <v>45809</v>
@@ -2814,13 +2814,13 @@
         <v>43</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -2839,16 +2839,16 @@
       </c>
       <c r="O29" s="5"/>
       <c r="P29" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q29" s="5">
+        <v>1</v>
+      </c>
+      <c r="R29" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="Q29" s="5">
-        <v>1</v>
-      </c>
-      <c r="R29" s="5" t="s">
+      <c r="S29" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="S29" s="5" t="s">
-        <v>100</v>
       </c>
       <c r="T29" s="5">
         <v>1</v>
@@ -2860,7 +2860,7 @@
       <c r="W29" s="5"/>
       <c r="X29" s="5"/>
       <c r="Y29" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Z29" s="6">
         <v>45809</v>
@@ -2887,16 +2887,16 @@
         <v>43</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E30" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F30" s="5" t="s">
         <v>103</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>104</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="K30" s="5"/>
       <c r="L30" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M30" s="5" t="s">
         <v>49</v>
@@ -2925,7 +2925,7 @@
         <v>51</v>
       </c>
       <c r="S30" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T30" s="5">
         <v>1</v>
@@ -2958,16 +2958,16 @@
         <v>43</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E31" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F31" s="5" t="s">
         <v>103</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>104</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="K31" s="5"/>
       <c r="L31" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M31" s="5" t="s">
         <v>49</v>
@@ -2996,7 +2996,7 @@
         <v>51</v>
       </c>
       <c r="S31" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T31" s="5">
         <v>1</v>
@@ -3029,16 +3029,16 @@
         <v>43</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F32" s="5" t="s">
         <v>103</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>104</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="K32" s="5"/>
       <c r="L32" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M32" s="5" t="s">
         <v>49</v>
@@ -3067,7 +3067,7 @@
         <v>51</v>
       </c>
       <c r="S32" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T32" s="5">
         <v>1</v>
@@ -3100,16 +3100,16 @@
         <v>43</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E33" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F33" s="5" t="s">
         <v>103</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>104</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="K33" s="5"/>
       <c r="L33" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M33" s="5" t="s">
         <v>49</v>
@@ -3138,7 +3138,7 @@
         <v>51</v>
       </c>
       <c r="S33" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T33" s="5">
         <v>1</v>
@@ -3171,16 +3171,16 @@
         <v>43</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E34" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F34" s="5" t="s">
         <v>103</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>104</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="K34" s="5"/>
       <c r="L34" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M34" s="5" t="s">
         <v>49</v>
@@ -3209,7 +3209,7 @@
         <v>51</v>
       </c>
       <c r="S34" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T34" s="5">
         <v>1</v>
@@ -3242,16 +3242,16 @@
         <v>43</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E35" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F35" s="5" t="s">
         <v>103</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>104</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="K35" s="5"/>
       <c r="L35" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M35" s="5" t="s">
         <v>49</v>
@@ -3280,7 +3280,7 @@
         <v>51</v>
       </c>
       <c r="S35" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T35" s="5">
         <v>1</v>
@@ -3313,16 +3313,16 @@
         <v>43</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E36" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F36" s="5" t="s">
         <v>103</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>104</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="K36" s="5"/>
       <c r="L36" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M36" s="5" t="s">
         <v>49</v>
@@ -3351,7 +3351,7 @@
         <v>51</v>
       </c>
       <c r="S36" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T36" s="5">
         <v>1</v>
@@ -3384,16 +3384,16 @@
         <v>43</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E37" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F37" s="5" t="s">
         <v>103</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>104</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="K37" s="5"/>
       <c r="L37" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M37" s="5" t="s">
         <v>49</v>
@@ -3422,7 +3422,7 @@
         <v>51</v>
       </c>
       <c r="S37" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T37" s="5">
         <v>1</v>
@@ -3455,16 +3455,16 @@
         <v>43</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E38" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F38" s="5" t="s">
         <v>103</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>104</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="K38" s="5"/>
       <c r="L38" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M38" s="5" t="s">
         <v>49</v>
@@ -3493,7 +3493,7 @@
         <v>51</v>
       </c>
       <c r="S38" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="T38" s="5">
         <v>1</v>
@@ -3526,16 +3526,16 @@
         <v>43</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E39" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F39" s="5" t="s">
         <v>103</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>104</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="K39" s="5"/>
       <c r="L39" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M39" s="5" t="s">
         <v>49</v>
@@ -3564,7 +3564,7 @@
         <v>51</v>
       </c>
       <c r="S39" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="T39" s="5">
         <v>1</v>
@@ -3606,7 +3606,7 @@
         <v>83</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5" t="s">
@@ -3619,7 +3619,7 @@
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
       <c r="M40" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N40" s="5"/>
       <c r="O40" s="5"/>
@@ -3651,13 +3651,13 @@
       <c r="AC40" s="5"/>
       <c r="AD40" s="5"/>
       <c r="AE40" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF40" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="AF40" s="5" t="s">
-        <v>115</v>
-      </c>
       <c r="AG40" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AH40" s="5"/>
       <c r="AI40" s="5"/>
@@ -3687,7 +3687,7 @@
         <v>83</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="5" t="s">
@@ -3700,7 +3700,7 @@
       <c r="K41" s="5"/>
       <c r="L41" s="5"/>
       <c r="M41" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N41" s="5"/>
       <c r="O41" s="5"/>
@@ -3714,7 +3714,7 @@
         <v>51</v>
       </c>
       <c r="S41" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T41" s="5">
         <v>1</v>
@@ -3732,13 +3732,13 @@
       <c r="AC41" s="5"/>
       <c r="AD41" s="5"/>
       <c r="AE41" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AF41" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="AG41" s="5" t="s">
         <v>115</v>
-      </c>
-      <c r="AG41" s="5" t="s">
-        <v>116</v>
       </c>
       <c r="AH41" s="5"/>
       <c r="AI41" s="5"/>
@@ -3759,16 +3759,16 @@
         <v>43</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5" t="s">
@@ -3781,7 +3781,7 @@
       <c r="K42" s="5"/>
       <c r="L42" s="5"/>
       <c r="M42" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N42" s="5"/>
       <c r="O42" s="5"/>
@@ -3813,13 +3813,13 @@
       <c r="AC42" s="5"/>
       <c r="AD42" s="5"/>
       <c r="AE42" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AF42" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG42" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AH42" s="5"/>
       <c r="AI42" s="5"/>
@@ -3840,16 +3840,16 @@
         <v>43</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5" t="s">
@@ -3862,7 +3862,7 @@
       <c r="K43" s="5"/>
       <c r="L43" s="5"/>
       <c r="M43" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N43" s="5"/>
       <c r="O43" s="5"/>
@@ -3876,7 +3876,7 @@
         <v>51</v>
       </c>
       <c r="S43" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T43" s="5">
         <v>1</v>
@@ -3894,13 +3894,13 @@
       <c r="AC43" s="5"/>
       <c r="AD43" s="5"/>
       <c r="AE43" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AF43" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG43" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AH43" s="5"/>
       <c r="AI43" s="5"/>
@@ -3930,7 +3930,7 @@
         <v>88</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5" t="s">
@@ -3943,7 +3943,7 @@
       <c r="K44" s="5"/>
       <c r="L44" s="5"/>
       <c r="M44" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N44" s="5"/>
       <c r="O44" s="5"/>
@@ -3975,13 +3975,13 @@
       <c r="AC44" s="5"/>
       <c r="AD44" s="5"/>
       <c r="AE44" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AF44" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG44" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AH44" s="5"/>
       <c r="AI44" s="5"/>
@@ -4011,7 +4011,7 @@
         <v>88</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5" t="s">
@@ -4024,7 +4024,7 @@
       <c r="K45" s="5"/>
       <c r="L45" s="5"/>
       <c r="M45" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N45" s="5"/>
       <c r="O45" s="5"/>
@@ -4038,7 +4038,7 @@
         <v>51</v>
       </c>
       <c r="S45" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T45" s="5">
         <v>1</v>
@@ -4056,13 +4056,13 @@
       <c r="AC45" s="5"/>
       <c r="AD45" s="5"/>
       <c r="AE45" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AF45" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG45" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AH45" s="5"/>
       <c r="AI45" s="5"/>
@@ -4092,7 +4092,7 @@
         <v>90</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5" t="s">
@@ -4105,7 +4105,7 @@
       <c r="K46" s="5"/>
       <c r="L46" s="5"/>
       <c r="M46" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N46" s="5"/>
       <c r="O46" s="5"/>
@@ -4137,13 +4137,13 @@
       <c r="AC46" s="5"/>
       <c r="AD46" s="5"/>
       <c r="AE46" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AF46" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG46" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AH46" s="5"/>
       <c r="AI46" s="5"/>
@@ -4173,7 +4173,7 @@
         <v>90</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5" t="s">
@@ -4186,7 +4186,7 @@
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
       <c r="M47" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N47" s="5"/>
       <c r="O47" s="5"/>
@@ -4200,7 +4200,7 @@
         <v>51</v>
       </c>
       <c r="S47" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T47" s="5">
         <v>1</v>
@@ -4218,13 +4218,13 @@
       <c r="AC47" s="5"/>
       <c r="AD47" s="5"/>
       <c r="AE47" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AF47" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG47" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AH47" s="5"/>
       <c r="AI47" s="5"/>
@@ -4245,16 +4245,16 @@
         <v>43</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5" t="s">
@@ -4267,7 +4267,7 @@
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
       <c r="M48" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N48" s="5"/>
       <c r="O48" s="5"/>
@@ -4299,13 +4299,13 @@
       <c r="AC48" s="5"/>
       <c r="AD48" s="5"/>
       <c r="AE48" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AF48" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG48" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AH48" s="5"/>
       <c r="AI48" s="5"/>
@@ -4335,7 +4335,7 @@
         <v>94</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5" t="s">
@@ -4348,7 +4348,7 @@
       <c r="K49" s="5"/>
       <c r="L49" s="5"/>
       <c r="M49" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N49" s="5"/>
       <c r="O49" s="5"/>
@@ -4380,13 +4380,13 @@
       <c r="AC49" s="5"/>
       <c r="AD49" s="5"/>
       <c r="AE49" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AF49" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG49" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AH49" s="5"/>
       <c r="AI49" s="5"/>
@@ -4416,7 +4416,7 @@
         <v>94</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5" t="s">
@@ -4429,7 +4429,7 @@
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
       <c r="M50" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N50" s="5"/>
       <c r="O50" s="5"/>
@@ -4443,7 +4443,7 @@
         <v>51</v>
       </c>
       <c r="S50" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T50" s="5">
         <v>1</v>
@@ -4461,13 +4461,13 @@
       <c r="AC50" s="5"/>
       <c r="AD50" s="5"/>
       <c r="AE50" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AF50" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG50" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AH50" s="5"/>
       <c r="AI50" s="5"/>

--- a/inst/extdata/fort_peck_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/fort_peck_tribe_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/sheila_saia_tetratech_com/Documents/Documents/github/TADACommunityHub/inst/extdata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{7332D495-FC66-4FCE-83BA-16794A495AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DCB93DD-570D-4326-8572-47CBBD4573F2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E382C649-F216-4A30-90E0-F2F0CA8F7E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A9D2C00B-42FB-4D75-83D9-FF6DA97293BD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A9D2C00B-42FB-4D75-83D9-FF6DA97293BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -326,9 +326,6 @@
     <t>ESCHERICHIA COLI</t>
   </si>
   <si>
-    <t>#/100mL</t>
-  </si>
-  <si>
     <t>n-season</t>
   </si>
   <si>
@@ -438,6 +435,9 @@
   </si>
   <si>
     <t>Jun-Sep</t>
+  </si>
+  <si>
+    <t>CFU/100ML</t>
   </si>
 </sst>
 </file>
@@ -850,23 +850,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48473D4D-2A67-413E-80AF-8677973F00EA}">
   <dimension ref="A1:AP50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="9.140625" style="5"/>
+    <col min="1" max="2" width="9.1796875" style="5"/>
     <col min="3" max="3" width="27" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.140625" style="5" customWidth="1"/>
-    <col min="6" max="17" width="9.140625" style="5"/>
-    <col min="18" max="18" width="15.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="20" max="24" width="9.140625" style="5"/>
-    <col min="25" max="25" width="16.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.140625" style="5"/>
-    <col min="27" max="27" width="10.7109375" style="5" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="5"/>
+    <col min="4" max="4" width="20.54296875" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.1796875" style="5" customWidth="1"/>
+    <col min="6" max="17" width="9.1796875" style="5"/>
+    <col min="18" max="18" width="15.1796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.7265625" style="5" bestFit="1" customWidth="1"/>
+    <col min="20" max="24" width="9.1796875" style="5"/>
+    <col min="25" max="25" width="16.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.1796875" style="5"/>
+    <col min="27" max="27" width="10.7265625" style="5" customWidth="1"/>
+    <col min="28" max="16384" width="9.1796875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:42" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -994,7 +994,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
         <v>42</v>
@@ -1062,7 +1062,7 @@
       <c r="AK2" s="3"/>
       <c r="AL2" s="3"/>
     </row>
-    <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
         <v>42</v>
@@ -1130,7 +1130,7 @@
       <c r="AK3" s="3"/>
       <c r="AL3" s="3"/>
     </row>
-    <row r="4" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
         <v>42</v>
@@ -1196,7 +1196,7 @@
       <c r="AK4" s="3"/>
       <c r="AL4" s="3"/>
     </row>
-    <row r="5" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
         <v>42</v>
@@ -1262,7 +1262,7 @@
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
     </row>
-    <row r="6" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
         <v>42</v>
@@ -1328,7 +1328,7 @@
       <c r="AK6" s="3"/>
       <c r="AL6" s="3"/>
     </row>
-    <row r="7" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
         <v>42</v>
@@ -1394,7 +1394,7 @@
       <c r="AK7" s="3"/>
       <c r="AL7" s="3"/>
     </row>
-    <row r="8" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
         <v>42</v>
@@ -1460,7 +1460,7 @@
       <c r="AK8" s="3"/>
       <c r="AL8" s="3"/>
     </row>
-    <row r="9" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
         <v>42</v>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>48</v>
@@ -1518,10 +1518,10 @@
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AF9" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AG9" s="3"/>
       <c r="AH9" s="3"/>
@@ -1530,7 +1530,7 @@
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
     </row>
-    <row r="10" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
         <v>42</v>
@@ -1596,7 +1596,7 @@
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
     </row>
-    <row r="11" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
         <v>42</v>
@@ -1662,7 +1662,7 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
         <v>42</v>
@@ -1726,7 +1726,7 @@
       <c r="AK12" s="3"/>
       <c r="AL12" s="3"/>
     </row>
-    <row r="13" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
         <v>42</v>
@@ -1790,7 +1790,7 @@
       <c r="AK13" s="3"/>
       <c r="AL13" s="3"/>
     </row>
-    <row r="14" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
         <v>42</v>
@@ -1854,7 +1854,7 @@
       <c r="AK14" s="3"/>
       <c r="AL14" s="3"/>
     </row>
-    <row r="15" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
         <v>42</v>
@@ -1918,7 +1918,7 @@
       <c r="AK15" s="3"/>
       <c r="AL15" s="3"/>
     </row>
-    <row r="16" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
         <v>42</v>
@@ -1982,7 +1982,7 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
         <v>42</v>
@@ -2046,7 +2046,7 @@
       <c r="AK17" s="3"/>
       <c r="AL17" s="3"/>
     </row>
-    <row r="18" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
         <v>42</v>
@@ -2110,7 +2110,7 @@
       <c r="AK18" s="3"/>
       <c r="AL18" s="3"/>
     </row>
-    <row r="19" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
         <v>42</v>
@@ -2174,7 +2174,7 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
         <v>42</v>
@@ -2238,7 +2238,7 @@
       <c r="AK20" s="3"/>
       <c r="AL20" s="3"/>
     </row>
-    <row r="21" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
         <v>42</v>
@@ -2302,7 +2302,7 @@
       <c r="AK21" s="3"/>
       <c r="AL21" s="3"/>
     </row>
-    <row r="22" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
         <v>42</v>
@@ -2366,7 +2366,7 @@
       <c r="AK22" s="3"/>
       <c r="AL22" s="3"/>
     </row>
-    <row r="23" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
         <v>42</v>
@@ -2430,7 +2430,7 @@
       <c r="AK23" s="3"/>
       <c r="AL23" s="3"/>
     </row>
-    <row r="24" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
         <v>42</v>
@@ -2496,16 +2496,16 @@
       <c r="AK24" s="3"/>
       <c r="AL24" s="3"/>
     </row>
-    <row r="25" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>94</v>
@@ -2529,16 +2529,16 @@
       </c>
       <c r="O25" s="3"/>
       <c r="P25" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>1</v>
+      </c>
+      <c r="R25" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="Q25" s="3">
-        <v>1</v>
-      </c>
-      <c r="R25" s="3" t="s">
+      <c r="S25" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="S25" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="T25" s="3">
         <v>1</v>
@@ -2550,13 +2550,13 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Z25" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA25" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="AA25" s="4" t="s">
-        <v>130</v>
       </c>
       <c r="AB25" s="3"/>
       <c r="AC25" s="3"/>
@@ -2570,13 +2570,13 @@
       <c r="AK25" s="3"/>
       <c r="AL25" s="3"/>
     </row>
-    <row r="26" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>44</v>
@@ -2603,16 +2603,16 @@
       </c>
       <c r="O26" s="3"/>
       <c r="P26" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>1</v>
+      </c>
+      <c r="R26" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="Q26" s="3">
-        <v>1</v>
-      </c>
-      <c r="R26" s="3" t="s">
+      <c r="S26" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="T26" s="3">
         <v>1</v>
@@ -2624,13 +2624,13 @@
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
       <c r="Y26" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Z26" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA26" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="AA26" s="4" t="s">
-        <v>130</v>
       </c>
       <c r="AB26" s="3"/>
       <c r="AC26" s="3"/>
@@ -2644,16 +2644,16 @@
       <c r="AK26" s="3"/>
       <c r="AL26" s="3"/>
     </row>
-    <row r="27" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>94</v>
@@ -2675,16 +2675,16 @@
       </c>
       <c r="O27" s="3"/>
       <c r="P27" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>1</v>
+      </c>
+      <c r="R27" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="Q27" s="3">
-        <v>1</v>
-      </c>
-      <c r="R27" s="3" t="s">
+      <c r="S27" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="T27" s="3">
         <v>1</v>
@@ -2696,13 +2696,13 @@
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
       <c r="Y27" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Z27" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA27" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="AA27" s="4" t="s">
-        <v>130</v>
       </c>
       <c r="AB27" s="3"/>
       <c r="AC27" s="3"/>
@@ -2716,13 +2716,13 @@
       <c r="AK27" s="3"/>
       <c r="AL27" s="3"/>
     </row>
-    <row r="28" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>44</v>
@@ -2747,16 +2747,16 @@
       </c>
       <c r="O28" s="3"/>
       <c r="P28" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>1</v>
+      </c>
+      <c r="R28" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="Q28" s="3">
-        <v>1</v>
-      </c>
-      <c r="R28" s="3" t="s">
+      <c r="S28" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="S28" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="T28" s="3">
         <v>1</v>
@@ -2768,13 +2768,13 @@
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Z28" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA28" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="AA28" s="4" t="s">
-        <v>130</v>
       </c>
       <c r="AB28" s="3"/>
       <c r="AC28" s="3"/>
@@ -2788,16 +2788,16 @@
       <c r="AK28" s="3"/>
       <c r="AL28" s="3"/>
     </row>
-    <row r="29" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>94</v>
@@ -2819,16 +2819,16 @@
       </c>
       <c r="O29" s="3"/>
       <c r="P29" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>1</v>
+      </c>
+      <c r="R29" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="Q29" s="3">
-        <v>1</v>
-      </c>
-      <c r="R29" s="3" t="s">
+      <c r="S29" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="T29" s="3">
         <v>1</v>
@@ -2840,13 +2840,13 @@
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
       <c r="Y29" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Z29" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA29" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="AA29" s="4" t="s">
-        <v>130</v>
       </c>
       <c r="AB29" s="3"/>
       <c r="AC29" s="3"/>
@@ -2860,22 +2860,22 @@
       <c r="AK29" s="3"/>
       <c r="AL29" s="3"/>
     </row>
-    <row r="30" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E30" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M30" s="3" t="s">
         <v>48</v>
@@ -2904,7 +2904,7 @@
         <v>50</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T30" s="3">
         <v>1</v>
@@ -2930,22 +2930,22 @@
       <c r="AK30" s="3"/>
       <c r="AL30" s="3"/>
     </row>
-    <row r="31" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E31" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M31" s="3" t="s">
         <v>48</v>
@@ -2974,7 +2974,7 @@
         <v>50</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T31" s="3">
         <v>1</v>
@@ -3000,22 +3000,22 @@
       <c r="AK31" s="3"/>
       <c r="AL31" s="3"/>
     </row>
-    <row r="32" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E32" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>48</v>
@@ -3044,7 +3044,7 @@
         <v>50</v>
       </c>
       <c r="S32" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T32" s="3">
         <v>1</v>
@@ -3070,22 +3070,22 @@
       <c r="AK32" s="3"/>
       <c r="AL32" s="3"/>
     </row>
-    <row r="33" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E33" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>48</v>
@@ -3114,7 +3114,7 @@
         <v>50</v>
       </c>
       <c r="S33" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T33" s="3">
         <v>1</v>
@@ -3140,22 +3140,22 @@
       <c r="AK33" s="3"/>
       <c r="AL33" s="3"/>
     </row>
-    <row r="34" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E34" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M34" s="3" t="s">
         <v>48</v>
@@ -3184,7 +3184,7 @@
         <v>50</v>
       </c>
       <c r="S34" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T34" s="3">
         <v>1</v>
@@ -3210,22 +3210,22 @@
       <c r="AK34" s="3"/>
       <c r="AL34" s="3"/>
     </row>
-    <row r="35" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E35" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>48</v>
@@ -3254,7 +3254,7 @@
         <v>50</v>
       </c>
       <c r="S35" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T35" s="3">
         <v>1</v>
@@ -3280,22 +3280,22 @@
       <c r="AK35" s="3"/>
       <c r="AL35" s="3"/>
     </row>
-    <row r="36" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E36" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M36" s="3" t="s">
         <v>48</v>
@@ -3324,7 +3324,7 @@
         <v>50</v>
       </c>
       <c r="S36" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T36" s="3">
         <v>1</v>
@@ -3350,22 +3350,22 @@
       <c r="AK36" s="3"/>
       <c r="AL36" s="3"/>
     </row>
-    <row r="37" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E37" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M37" s="3" t="s">
         <v>48</v>
@@ -3394,7 +3394,7 @@
         <v>50</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T37" s="3">
         <v>1</v>
@@ -3420,22 +3420,22 @@
       <c r="AK37" s="3"/>
       <c r="AL37" s="3"/>
     </row>
-    <row r="38" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E38" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M38" s="3" t="s">
         <v>48</v>
@@ -3464,7 +3464,7 @@
         <v>50</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T38" s="3">
         <v>1</v>
@@ -3490,22 +3490,22 @@
       <c r="AK38" s="3"/>
       <c r="AL38" s="3"/>
     </row>
-    <row r="39" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E39" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M39" s="3" t="s">
         <v>48</v>
@@ -3534,7 +3534,7 @@
         <v>50</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T39" s="3">
         <v>1</v>
@@ -3560,7 +3560,7 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
         <v>42</v>
@@ -3575,7 +3575,7 @@
         <v>81</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3" t="s">
@@ -3588,7 +3588,7 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
@@ -3620,10 +3620,10 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF40" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
         <v>42</v>
@@ -3653,7 +3653,7 @@
         <v>81</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3" t="s">
@@ -3666,7 +3666,7 @@
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N41" s="3"/>
       <c r="O41" s="3"/>
@@ -3680,7 +3680,7 @@
         <v>50</v>
       </c>
       <c r="S41" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T41" s="3">
         <v>1</v>
@@ -3698,10 +3698,10 @@
       <c r="AC41" s="3"/>
       <c r="AD41" s="3"/>
       <c r="AE41" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF41" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="AF41" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="AG41" s="3"/>
       <c r="AH41" s="3"/>
@@ -3716,22 +3716,22 @@
       </c>
       <c r="AL41" s="3"/>
     </row>
-    <row r="42" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3" t="s">
@@ -3744,7 +3744,7 @@
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N42" s="3"/>
       <c r="O42" s="3"/>
@@ -3776,10 +3776,10 @@
       <c r="AC42" s="3"/>
       <c r="AD42" s="3"/>
       <c r="AE42" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF42" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AG42" s="3"/>
       <c r="AH42" s="3"/>
@@ -3794,22 +3794,22 @@
       </c>
       <c r="AL42" s="3"/>
     </row>
-    <row r="43" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3" t="s">
@@ -3822,7 +3822,7 @@
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N43" s="3"/>
       <c r="O43" s="3"/>
@@ -3836,7 +3836,7 @@
         <v>50</v>
       </c>
       <c r="S43" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T43" s="3">
         <v>1</v>
@@ -3854,10 +3854,10 @@
       <c r="AC43" s="3"/>
       <c r="AD43" s="3"/>
       <c r="AE43" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF43" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG43" s="3"/>
       <c r="AH43" s="3"/>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="AL43" s="3"/>
     </row>
-    <row r="44" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
         <v>42</v>
@@ -3887,7 +3887,7 @@
         <v>86</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G44" s="3"/>
       <c r="H44" s="3" t="s">
@@ -3900,7 +3900,7 @@
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N44" s="3"/>
       <c r="O44" s="3"/>
@@ -3932,10 +3932,10 @@
       <c r="AC44" s="3"/>
       <c r="AD44" s="3"/>
       <c r="AE44" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF44" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG44" s="3"/>
       <c r="AH44" s="3"/>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="AL44" s="3"/>
     </row>
-    <row r="45" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
         <v>42</v>
@@ -3965,7 +3965,7 @@
         <v>86</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="3" t="s">
@@ -3978,7 +3978,7 @@
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
@@ -3992,7 +3992,7 @@
         <v>50</v>
       </c>
       <c r="S45" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T45" s="3">
         <v>1</v>
@@ -4010,10 +4010,10 @@
       <c r="AC45" s="3"/>
       <c r="AD45" s="3"/>
       <c r="AE45" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF45" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AG45" s="3"/>
       <c r="AH45" s="3"/>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="AL45" s="3"/>
     </row>
-    <row r="46" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
         <v>42</v>
@@ -4043,7 +4043,7 @@
         <v>88</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3" t="s">
@@ -4056,7 +4056,7 @@
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
@@ -4088,10 +4088,10 @@
       <c r="AC46" s="3"/>
       <c r="AD46" s="3"/>
       <c r="AE46" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF46" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AG46" s="3"/>
       <c r="AH46" s="3"/>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AL46" s="3"/>
     </row>
-    <row r="47" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
         <v>42</v>
@@ -4121,7 +4121,7 @@
         <v>88</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="3" t="s">
@@ -4134,7 +4134,7 @@
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
@@ -4148,7 +4148,7 @@
         <v>50</v>
       </c>
       <c r="S47" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T47" s="3">
         <v>1</v>
@@ -4166,10 +4166,10 @@
       <c r="AC47" s="3"/>
       <c r="AD47" s="3"/>
       <c r="AE47" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF47" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG47" s="3"/>
       <c r="AH47" s="3"/>
@@ -4184,22 +4184,22 @@
       </c>
       <c r="AL47" s="3"/>
     </row>
-    <row r="48" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3" t="s">
@@ -4212,7 +4212,7 @@
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
@@ -4244,10 +4244,10 @@
       <c r="AC48" s="3"/>
       <c r="AD48" s="3"/>
       <c r="AE48" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF48" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG48" s="3"/>
       <c r="AH48" s="3"/>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="AL48" s="3"/>
     </row>
-    <row r="49" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
         <v>42</v>
@@ -4277,7 +4277,7 @@
         <v>92</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3" t="s">
@@ -4290,7 +4290,7 @@
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N49" s="3"/>
       <c r="O49" s="3"/>
@@ -4322,10 +4322,10 @@
       <c r="AC49" s="3"/>
       <c r="AD49" s="3"/>
       <c r="AE49" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF49" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG49" s="3"/>
       <c r="AH49" s="3"/>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="AL49" s="3"/>
     </row>
-    <row r="50" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
         <v>42</v>
@@ -4355,7 +4355,7 @@
         <v>92</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="3" t="s">
@@ -4368,7 +4368,7 @@
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="3"/>
@@ -4382,7 +4382,7 @@
         <v>50</v>
       </c>
       <c r="S50" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T50" s="3">
         <v>1</v>
@@ -4400,10 +4400,10 @@
       <c r="AC50" s="3"/>
       <c r="AD50" s="3"/>
       <c r="AE50" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF50" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG50" s="3"/>
       <c r="AH50" s="3"/>

--- a/inst/extdata/fort_peck_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/fort_peck_tribe_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E382C649-F216-4A30-90E0-F2F0CA8F7E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F0DC3D-5790-4B74-910A-1FBDBD12360F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A9D2C00B-42FB-4D75-83D9-FF6DA97293BD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{A9D2C00B-42FB-4D75-83D9-FF6DA97293BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -134,9 +134,6 @@
     <t>EquationType</t>
   </si>
   <si>
-    <t>Equation</t>
-  </si>
-  <si>
     <t>hardness_param_1</t>
   </si>
   <si>
@@ -438,6 +435,9 @@
   </si>
   <si>
     <t>CFU/100ML</t>
+  </si>
+  <si>
+    <t>EquationFormula</t>
   </si>
 </sst>
 </file>
@@ -850,23 +850,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48473D4D-2A67-413E-80AF-8677973F00EA}">
   <dimension ref="A1:AP50"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.1796875" style="5"/>
+    <col min="1" max="2" width="9.140625" style="5"/>
     <col min="3" max="3" width="27" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.54296875" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.1796875" style="5" customWidth="1"/>
-    <col min="6" max="17" width="9.1796875" style="5"/>
-    <col min="18" max="18" width="15.1796875" style="5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19.7265625" style="5" bestFit="1" customWidth="1"/>
-    <col min="20" max="24" width="9.1796875" style="5"/>
-    <col min="25" max="25" width="16.81640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.1796875" style="5"/>
-    <col min="27" max="27" width="10.7265625" style="5" customWidth="1"/>
-    <col min="28" max="16384" width="9.1796875" style="5"/>
+    <col min="4" max="4" width="20.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.140625" style="5" customWidth="1"/>
+    <col min="6" max="17" width="9.140625" style="5"/>
+    <col min="18" max="18" width="15.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="20" max="24" width="9.140625" style="5"/>
+    <col min="25" max="25" width="16.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.140625" style="5"/>
+    <col min="27" max="27" width="10.7109375" style="5" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="46.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:42" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -961,66 +961,66 @@
         <v>30</v>
       </c>
       <c r="AF1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="AG1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AK1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K2" s="3"/>
       <c r="L2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="N2" s="3">
         <v>6.5</v>
@@ -1029,20 +1029,20 @@
         <v>9</v>
       </c>
       <c r="P2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>1</v>
+      </c>
+      <c r="R2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="Q2" s="3">
-        <v>1</v>
-      </c>
-      <c r="R2" s="3" t="s">
+      <c r="S2" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="T2" s="3"/>
       <c r="U2" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
@@ -1062,33 +1062,33 @@
       <c r="AK2" s="3"/>
       <c r="AL2" s="3"/>
     </row>
-    <row r="3" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N3" s="3">
         <v>6.5</v>
@@ -1097,20 +1097,20 @@
         <v>9</v>
       </c>
       <c r="P3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>1</v>
+      </c>
+      <c r="R3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="Q3" s="3">
-        <v>1</v>
-      </c>
-      <c r="R3" s="3" t="s">
+      <c r="S3" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="T3" s="3"/>
       <c r="U3" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
@@ -1130,53 +1130,53 @@
       <c r="AK3" s="3"/>
       <c r="AL3" s="3"/>
     </row>
-    <row r="4" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="N4" s="3">
         <v>27</v>
       </c>
       <c r="O4" s="3"/>
       <c r="P4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>1</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="S4" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="Q4" s="3">
-        <v>1</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
@@ -1196,53 +1196,53 @@
       <c r="AK4" s="3"/>
       <c r="AL4" s="3"/>
     </row>
-    <row r="5" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N5" s="3">
         <v>23</v>
       </c>
       <c r="O5" s="3"/>
       <c r="P5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>1</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="S5" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="Q5" s="3">
-        <v>1</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="T5" s="3"/>
       <c r="U5" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
@@ -1262,53 +1262,53 @@
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
     </row>
-    <row r="6" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N6" s="3">
         <v>860000</v>
       </c>
       <c r="O6" s="3"/>
       <c r="P6" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q6" s="3">
         <v>1</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T6" s="3"/>
       <c r="U6" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
@@ -1328,53 +1328,53 @@
       <c r="AK6" s="3"/>
       <c r="AL6" s="3"/>
     </row>
-    <row r="7" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N7" s="3">
         <v>230000</v>
       </c>
       <c r="O7" s="3"/>
       <c r="P7" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q7" s="3">
         <v>1</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T7" s="3"/>
       <c r="U7" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
@@ -1394,53 +1394,53 @@
       <c r="AK7" s="3"/>
       <c r="AL7" s="3"/>
     </row>
-    <row r="8" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N8" s="3">
         <v>20</v>
       </c>
       <c r="O8" s="3"/>
       <c r="P8" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q8" s="3">
         <v>1</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T8" s="3"/>
       <c r="U8" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
@@ -1460,53 +1460,53 @@
       <c r="AK8" s="3"/>
       <c r="AL8" s="3"/>
     </row>
-    <row r="9" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N9" s="3">
         <v>17</v>
       </c>
       <c r="O9" s="3"/>
       <c r="P9" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q9" s="3">
         <v>1</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
@@ -1518,10 +1518,10 @@
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AF9" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AG9" s="3"/>
       <c r="AH9" s="3"/>
@@ -1530,53 +1530,53 @@
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
     </row>
-    <row r="10" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N10" s="3">
         <v>1.3</v>
       </c>
       <c r="O10" s="3"/>
       <c r="P10" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q10" s="3">
         <v>1</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
@@ -1596,53 +1596,53 @@
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
     </row>
-    <row r="11" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N11" s="3">
         <v>0.3</v>
       </c>
       <c r="O11" s="3"/>
       <c r="P11" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q11" s="3">
         <v>1</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T11" s="3"/>
       <c r="U11" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
@@ -1662,51 +1662,51 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>70</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N12" s="3">
         <v>110</v>
       </c>
       <c r="O12" s="3"/>
       <c r="P12" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q12" s="3">
         <v>1</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T12" s="3"/>
       <c r="U12" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
@@ -1726,51 +1726,51 @@
       <c r="AK12" s="3"/>
       <c r="AL12" s="3"/>
     </row>
-    <row r="13" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N13" s="3">
         <v>750</v>
       </c>
       <c r="O13" s="3"/>
       <c r="P13" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q13" s="3">
         <v>1</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T13" s="3"/>
       <c r="U13" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
@@ -1790,51 +1790,51 @@
       <c r="AK13" s="3"/>
       <c r="AL13" s="3"/>
     </row>
-    <row r="14" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N14" s="3">
         <v>300</v>
       </c>
       <c r="O14" s="3"/>
       <c r="P14" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q14" s="3">
         <v>1</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T14" s="3"/>
       <c r="U14" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
@@ -1854,51 +1854,51 @@
       <c r="AK14" s="3"/>
       <c r="AL14" s="3"/>
     </row>
-    <row r="15" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N15" s="3">
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="O15" s="3"/>
       <c r="P15" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q15" s="3">
         <v>1</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T15" s="3"/>
       <c r="U15" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
@@ -1918,51 +1918,51 @@
       <c r="AK15" s="3"/>
       <c r="AL15" s="3"/>
     </row>
-    <row r="16" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N16" s="3">
         <v>1000</v>
       </c>
       <c r="O16" s="3"/>
       <c r="P16" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q16" s="3">
         <v>1</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
@@ -1982,51 +1982,51 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N17" s="3">
         <v>5</v>
       </c>
       <c r="O17" s="3"/>
       <c r="P17" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q17" s="3">
         <v>1</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T17" s="3"/>
       <c r="U17" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
@@ -2046,51 +2046,51 @@
       <c r="AK17" s="3"/>
       <c r="AL17" s="3"/>
     </row>
-    <row r="18" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N18" s="3">
         <v>1300</v>
       </c>
       <c r="O18" s="3"/>
       <c r="P18" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q18" s="3">
         <v>1</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T18" s="3"/>
       <c r="U18" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
@@ -2110,51 +2110,51 @@
       <c r="AK18" s="3"/>
       <c r="AL18" s="3"/>
     </row>
-    <row r="19" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N19" s="3">
         <v>4000</v>
       </c>
       <c r="O19" s="3"/>
       <c r="P19" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q19" s="3">
         <v>1</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T19" s="3"/>
       <c r="U19" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
@@ -2174,51 +2174,51 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N20" s="3">
         <v>300</v>
       </c>
       <c r="O20" s="3"/>
       <c r="P20" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q20" s="3">
         <v>1</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T20" s="3"/>
       <c r="U20" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
@@ -2238,51 +2238,51 @@
       <c r="AK20" s="3"/>
       <c r="AL20" s="3"/>
     </row>
-    <row r="21" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N21" s="3">
         <v>15</v>
       </c>
       <c r="O21" s="3"/>
       <c r="P21" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q21" s="3">
         <v>1</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T21" s="3"/>
       <c r="U21" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
@@ -2302,51 +2302,51 @@
       <c r="AK21" s="3"/>
       <c r="AL21" s="3"/>
     </row>
-    <row r="22" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N22" s="3">
         <v>610</v>
       </c>
       <c r="O22" s="3"/>
       <c r="P22" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q22" s="3">
         <v>1</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T22" s="3"/>
       <c r="U22" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
@@ -2366,51 +2366,51 @@
       <c r="AK22" s="3"/>
       <c r="AL22" s="3"/>
     </row>
-    <row r="23" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N23" s="3">
         <v>50</v>
       </c>
       <c r="O23" s="3"/>
       <c r="P23" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q23" s="3">
         <v>1</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T23" s="3"/>
       <c r="U23" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
@@ -2430,53 +2430,53 @@
       <c r="AK23" s="3"/>
       <c r="AL23" s="3"/>
     </row>
-    <row r="24" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>92</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N24" s="3">
         <v>7400</v>
       </c>
       <c r="O24" s="3"/>
       <c r="P24" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q24" s="3">
         <v>1</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T24" s="3">
         <v>1</v>
       </c>
       <c r="U24" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
@@ -2496,67 +2496,67 @@
       <c r="AK24" s="3"/>
       <c r="AL24" s="3"/>
     </row>
-    <row r="25" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N25" s="3">
         <v>235</v>
       </c>
       <c r="O25" s="3"/>
       <c r="P25" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q25" s="3">
         <v>1</v>
       </c>
       <c r="R25" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="S25" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="S25" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="T25" s="3">
         <v>1</v>
       </c>
       <c r="U25" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Z25" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA25" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="AA25" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="AB25" s="3"/>
       <c r="AC25" s="3"/>
@@ -2570,67 +2570,67 @@
       <c r="AK25" s="3"/>
       <c r="AL25" s="3"/>
     </row>
-    <row r="26" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N26" s="3">
         <v>235</v>
       </c>
       <c r="O26" s="3"/>
       <c r="P26" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q26" s="3">
         <v>1</v>
       </c>
       <c r="R26" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="S26" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="T26" s="3">
         <v>1</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
       <c r="Y26" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Z26" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA26" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="AA26" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="AB26" s="3"/>
       <c r="AC26" s="3"/>
@@ -2644,65 +2644,65 @@
       <c r="AK26" s="3"/>
       <c r="AL26" s="3"/>
     </row>
-    <row r="27" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N27" s="3">
         <v>126</v>
       </c>
       <c r="O27" s="3"/>
       <c r="P27" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q27" s="3">
         <v>1</v>
       </c>
       <c r="R27" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="S27" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="T27" s="3">
         <v>1</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
       <c r="Y27" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Z27" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA27" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="AA27" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="AB27" s="3"/>
       <c r="AC27" s="3"/>
@@ -2716,65 +2716,65 @@
       <c r="AK27" s="3"/>
       <c r="AL27" s="3"/>
     </row>
-    <row r="28" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N28" s="3">
         <v>126</v>
       </c>
       <c r="O28" s="3"/>
       <c r="P28" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q28" s="3">
         <v>1</v>
       </c>
       <c r="R28" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="S28" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="S28" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="T28" s="3">
         <v>1</v>
       </c>
       <c r="U28" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Z28" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA28" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="AA28" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="AB28" s="3"/>
       <c r="AC28" s="3"/>
@@ -2788,65 +2788,65 @@
       <c r="AK28" s="3"/>
       <c r="AL28" s="3"/>
     </row>
-    <row r="29" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N29" s="3">
         <v>126</v>
       </c>
       <c r="O29" s="3"/>
       <c r="P29" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q29" s="3">
         <v>1</v>
       </c>
       <c r="R29" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="S29" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="T29" s="3">
         <v>1</v>
       </c>
       <c r="U29" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
       <c r="Y29" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Z29" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA29" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="AA29" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="AB29" s="3"/>
       <c r="AC29" s="3"/>
@@ -2860,57 +2860,57 @@
       <c r="AK29" s="3"/>
       <c r="AL29" s="3"/>
     </row>
-    <row r="30" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E30" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N30" s="3">
         <v>6.5</v>
       </c>
       <c r="O30" s="3"/>
       <c r="P30" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q30" s="3">
         <v>30</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T30" s="3">
         <v>1</v>
       </c>
       <c r="U30" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
@@ -2930,57 +2930,57 @@
       <c r="AK30" s="3"/>
       <c r="AL30" s="3"/>
     </row>
-    <row r="31" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E31" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N31" s="3">
         <v>5.5</v>
       </c>
       <c r="O31" s="3"/>
       <c r="P31" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q31" s="3">
         <v>30</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T31" s="3">
         <v>1</v>
       </c>
       <c r="U31" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
@@ -3000,57 +3000,57 @@
       <c r="AK31" s="3"/>
       <c r="AL31" s="3"/>
     </row>
-    <row r="32" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E32" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N32" s="3">
         <v>9.5</v>
       </c>
       <c r="O32" s="3"/>
       <c r="P32" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q32" s="3">
         <v>7</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S32" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T32" s="3">
         <v>1</v>
       </c>
       <c r="U32" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
@@ -3070,57 +3070,57 @@
       <c r="AK32" s="3"/>
       <c r="AL32" s="3"/>
     </row>
-    <row r="33" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E33" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N33" s="3">
         <v>6</v>
       </c>
       <c r="O33" s="3"/>
       <c r="P33" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q33" s="3">
         <v>7</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S33" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T33" s="3">
         <v>1</v>
       </c>
       <c r="U33" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
@@ -3140,57 +3140,57 @@
       <c r="AK33" s="3"/>
       <c r="AL33" s="3"/>
     </row>
-    <row r="34" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E34" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N34" s="3">
         <v>8</v>
       </c>
       <c r="O34" s="3"/>
       <c r="P34" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q34" s="3">
         <v>1</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S34" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T34" s="3">
         <v>1</v>
       </c>
       <c r="U34" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
@@ -3210,57 +3210,57 @@
       <c r="AK34" s="3"/>
       <c r="AL34" s="3"/>
     </row>
-    <row r="35" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E35" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N35" s="3">
         <v>4</v>
       </c>
       <c r="O35" s="3"/>
       <c r="P35" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q35" s="3">
         <v>1</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S35" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T35" s="3">
         <v>1</v>
       </c>
       <c r="U35" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
@@ -3280,57 +3280,57 @@
       <c r="AK35" s="3"/>
       <c r="AL35" s="3"/>
     </row>
-    <row r="36" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E36" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N36" s="3">
         <v>5</v>
       </c>
       <c r="O36" s="3"/>
       <c r="P36" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q36" s="3">
         <v>1</v>
       </c>
       <c r="R36" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S36" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T36" s="3">
         <v>1</v>
       </c>
       <c r="U36" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
@@ -3350,57 +3350,57 @@
       <c r="AK36" s="3"/>
       <c r="AL36" s="3"/>
     </row>
-    <row r="37" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E37" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N37" s="3">
         <v>3</v>
       </c>
       <c r="O37" s="3"/>
       <c r="P37" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q37" s="3">
         <v>1</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T37" s="3">
         <v>1</v>
       </c>
       <c r="U37" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
@@ -3420,57 +3420,57 @@
       <c r="AK37" s="3"/>
       <c r="AL37" s="3"/>
     </row>
-    <row r="38" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E38" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N38" s="3">
         <v>5</v>
       </c>
       <c r="O38" s="3"/>
       <c r="P38" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q38" s="3">
         <v>7</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T38" s="3">
         <v>1</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
@@ -3490,57 +3490,57 @@
       <c r="AK38" s="3"/>
       <c r="AL38" s="3"/>
     </row>
-    <row r="39" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E39" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N39" s="3">
         <v>4</v>
       </c>
       <c r="O39" s="3"/>
       <c r="P39" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q39" s="3">
         <v>7</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T39" s="3">
         <v>1</v>
       </c>
       <c r="U39" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
@@ -3560,55 +3560,55 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C40" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="F40" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q40" s="3">
         <v>1</v>
       </c>
       <c r="R40" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S40" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T40" s="3">
         <v>1</v>
       </c>
       <c r="U40" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
@@ -3620,10 +3620,10 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AF40" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
@@ -3638,55 +3638,55 @@
       </c>
       <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C41" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E41" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="F41" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N41" s="3"/>
       <c r="O41" s="3"/>
       <c r="P41" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q41" s="3">
         <v>30</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S41" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T41" s="3">
         <v>1</v>
       </c>
       <c r="U41" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
@@ -3698,10 +3698,10 @@
       <c r="AC41" s="3"/>
       <c r="AD41" s="3"/>
       <c r="AE41" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF41" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="AF41" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="AG41" s="3"/>
       <c r="AH41" s="3"/>
@@ -3716,55 +3716,55 @@
       </c>
       <c r="AL41" s="3"/>
     </row>
-    <row r="42" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N42" s="3"/>
       <c r="O42" s="3"/>
       <c r="P42" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q42" s="3">
         <v>1</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S42" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T42" s="3">
         <v>1</v>
       </c>
       <c r="U42" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
@@ -3776,10 +3776,10 @@
       <c r="AC42" s="3"/>
       <c r="AD42" s="3"/>
       <c r="AE42" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AF42" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG42" s="3"/>
       <c r="AH42" s="3"/>
@@ -3794,55 +3794,55 @@
       </c>
       <c r="AL42" s="3"/>
     </row>
-    <row r="43" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N43" s="3"/>
       <c r="O43" s="3"/>
       <c r="P43" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q43" s="3">
         <v>30</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S43" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T43" s="3">
         <v>1</v>
       </c>
       <c r="U43" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3"/>
@@ -3854,10 +3854,10 @@
       <c r="AC43" s="3"/>
       <c r="AD43" s="3"/>
       <c r="AE43" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AF43" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AG43" s="3"/>
       <c r="AH43" s="3"/>
@@ -3872,55 +3872,55 @@
       </c>
       <c r="AL43" s="3"/>
     </row>
-    <row r="44" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C44" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E44" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="F44" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G44" s="3"/>
       <c r="H44" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I44" s="3"/>
       <c r="J44" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N44" s="3"/>
       <c r="O44" s="3"/>
       <c r="P44" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q44" s="3">
         <v>1</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S44" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T44" s="3">
         <v>1</v>
       </c>
       <c r="U44" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
@@ -3932,10 +3932,10 @@
       <c r="AC44" s="3"/>
       <c r="AD44" s="3"/>
       <c r="AE44" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AF44" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG44" s="3"/>
       <c r="AH44" s="3"/>
@@ -3950,55 +3950,55 @@
       </c>
       <c r="AL44" s="3"/>
     </row>
-    <row r="45" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C45" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E45" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="F45" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q45" s="3">
         <v>30</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S45" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T45" s="3">
         <v>1</v>
       </c>
       <c r="U45" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V45" s="3"/>
       <c r="W45" s="3"/>
@@ -4010,10 +4010,10 @@
       <c r="AC45" s="3"/>
       <c r="AD45" s="3"/>
       <c r="AE45" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AF45" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG45" s="3"/>
       <c r="AH45" s="3"/>
@@ -4028,55 +4028,55 @@
       </c>
       <c r="AL45" s="3"/>
     </row>
-    <row r="46" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C46" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E46" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="F46" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
       <c r="P46" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q46" s="3">
         <v>1</v>
       </c>
       <c r="R46" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S46" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T46" s="3">
         <v>1</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
@@ -4088,10 +4088,10 @@
       <c r="AC46" s="3"/>
       <c r="AD46" s="3"/>
       <c r="AE46" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AF46" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AG46" s="3"/>
       <c r="AH46" s="3"/>
@@ -4106,55 +4106,55 @@
       </c>
       <c r="AL46" s="3"/>
     </row>
-    <row r="47" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C47" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="F47" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
       <c r="P47" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q47" s="3">
         <v>30</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S47" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T47" s="3">
         <v>1</v>
       </c>
       <c r="U47" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
@@ -4166,10 +4166,10 @@
       <c r="AC47" s="3"/>
       <c r="AD47" s="3"/>
       <c r="AE47" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AF47" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AG47" s="3"/>
       <c r="AH47" s="3"/>
@@ -4184,55 +4184,55 @@
       </c>
       <c r="AL47" s="3"/>
     </row>
-    <row r="48" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C48" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="F48" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I48" s="3"/>
       <c r="J48" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
       <c r="P48" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q48" s="3">
         <v>1</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T48" s="3">
         <v>1</v>
       </c>
       <c r="U48" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
@@ -4244,10 +4244,10 @@
       <c r="AC48" s="3"/>
       <c r="AD48" s="3"/>
       <c r="AE48" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AF48" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AG48" s="3"/>
       <c r="AH48" s="3"/>
@@ -4262,55 +4262,55 @@
       </c>
       <c r="AL48" s="3"/>
     </row>
-    <row r="49" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C49" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="F49" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I49" s="3"/>
       <c r="J49" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N49" s="3"/>
       <c r="O49" s="3"/>
       <c r="P49" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q49" s="3">
         <v>1</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S49" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T49" s="3">
         <v>1</v>
       </c>
       <c r="U49" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="3"/>
@@ -4322,10 +4322,10 @@
       <c r="AC49" s="3"/>
       <c r="AD49" s="3"/>
       <c r="AE49" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AF49" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG49" s="3"/>
       <c r="AH49" s="3"/>
@@ -4340,55 +4340,55 @@
       </c>
       <c r="AL49" s="3"/>
     </row>
-    <row r="50" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C50" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E50" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="F50" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I50" s="3"/>
       <c r="J50" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="3"/>
       <c r="P50" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q50" s="3">
         <v>30</v>
       </c>
       <c r="R50" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S50" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T50" s="3">
         <v>1</v>
       </c>
       <c r="U50" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
@@ -4400,10 +4400,10 @@
       <c r="AC50" s="3"/>
       <c r="AD50" s="3"/>
       <c r="AE50" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AF50" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG50" s="3"/>
       <c r="AH50" s="3"/>

--- a/inst/extdata/fort_peck_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/fort_peck_tribe_criteria_crosswalk.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/hannah_ferriby_tetratech_com/Documents/Documents/GitHub/TADACommunityHub/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F0DC3D-5790-4B74-910A-1FBDBD12360F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{F4F0DC3D-5790-4B74-910A-1FBDBD12360F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{283FD004-495A-4A47-9967-A5E4A4E01251}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{A9D2C00B-42FB-4D75-83D9-FF6DA97293BD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A9D2C00B-42FB-4D75-83D9-FF6DA97293BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AP$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AR$50</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="140">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -146,12 +146,6 @@
     <t>hardness_param_4</t>
   </si>
   <si>
-    <t>hardness_param_5</t>
-  </si>
-  <si>
-    <t>hardness_param_6</t>
-  </si>
-  <si>
     <t>pH_param_1</t>
   </si>
   <si>
@@ -428,23 +422,50 @@
     <t>Sep 30</t>
   </si>
   <si>
-    <t>Additional Information</t>
-  </si>
-  <si>
     <t>Jun-Sep</t>
   </si>
   <si>
     <t>CFU/100ML</t>
   </si>
   <si>
-    <t>EquationFormula</t>
+    <t>Equation</t>
+  </si>
+  <si>
+    <t>pHThreshold</t>
+  </si>
+  <si>
+    <t>pHDirection</t>
+  </si>
+  <si>
+    <t>TemperatureExtreme</t>
+  </si>
+  <si>
+    <t>pH_param_5</t>
+  </si>
+  <si>
+    <t>pH_param_6</t>
+  </si>
+  <si>
+    <t>pH_param_7</t>
+  </si>
+  <si>
+    <t>pH_param_8</t>
+  </si>
+  <si>
+    <t>pH_param_9</t>
+  </si>
+  <si>
+    <t>MinEqMagnitude</t>
+  </si>
+  <si>
+    <t>MaxEqMagnitude</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -477,6 +498,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -498,7 +526,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -513,6 +541,9 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -849,7 +880,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48473D4D-2A67-413E-80AF-8677973F00EA}">
-  <dimension ref="A1:AP50"/>
+  <dimension ref="A1:AX50"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="5"/>
@@ -866,7 +897,7 @@
     <col min="28" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:50" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -961,66 +992,90 @@
         <v>30</v>
       </c>
       <c r="AF1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM1" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="AG1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AJ1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AO1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AR1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AW1" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX1" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K2" s="3"/>
       <c r="L2" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N2" s="3">
         <v>6.5</v>
@@ -1029,20 +1084,20 @@
         <v>9</v>
       </c>
       <c r="P2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>1</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S2" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>1</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="T2" s="3"/>
       <c r="U2" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
@@ -1061,34 +1116,36 @@
       <c r="AJ2" s="3"/>
       <c r="AK2" s="3"/>
       <c r="AL2" s="3"/>
-    </row>
-    <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM2" s="3"/>
+      <c r="AN2" s="3"/>
+    </row>
+    <row r="3" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N3" s="3">
         <v>6.5</v>
@@ -1097,20 +1154,20 @@
         <v>9</v>
       </c>
       <c r="P3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>1</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S3" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="Q3" s="3">
-        <v>1</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="T3" s="3"/>
       <c r="U3" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
@@ -1129,54 +1186,56 @@
       <c r="AJ3" s="3"/>
       <c r="AK3" s="3"/>
       <c r="AL3" s="3"/>
-    </row>
-    <row r="4" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM3" s="3"/>
+      <c r="AN3" s="3"/>
+    </row>
+    <row r="4" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E4" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N4" s="3">
         <v>27</v>
       </c>
       <c r="O4" s="3"/>
       <c r="P4" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q4" s="3">
         <v>1</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
@@ -1195,54 +1254,56 @@
       <c r="AJ4" s="3"/>
       <c r="AK4" s="3"/>
       <c r="AL4" s="3"/>
-    </row>
-    <row r="5" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM4" s="3"/>
+      <c r="AN4" s="3"/>
+    </row>
+    <row r="5" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E5" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N5" s="3">
         <v>23</v>
       </c>
       <c r="O5" s="3"/>
       <c r="P5" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q5" s="3">
         <v>1</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T5" s="3"/>
       <c r="U5" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
@@ -1261,54 +1322,56 @@
       <c r="AJ5" s="3"/>
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
-    </row>
-    <row r="6" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM5" s="3"/>
+      <c r="AN5" s="3"/>
+    </row>
+    <row r="6" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E6" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N6" s="3">
         <v>860000</v>
       </c>
       <c r="O6" s="3"/>
       <c r="P6" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q6" s="3">
         <v>1</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T6" s="3"/>
       <c r="U6" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
@@ -1327,54 +1390,56 @@
       <c r="AJ6" s="3"/>
       <c r="AK6" s="3"/>
       <c r="AL6" s="3"/>
-    </row>
-    <row r="7" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM6" s="3"/>
+      <c r="AN6" s="3"/>
+    </row>
+    <row r="7" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E7" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N7" s="3">
         <v>230000</v>
       </c>
       <c r="O7" s="3"/>
       <c r="P7" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q7" s="3">
         <v>1</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T7" s="3"/>
       <c r="U7" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
@@ -1393,54 +1458,56 @@
       <c r="AJ7" s="3"/>
       <c r="AK7" s="3"/>
       <c r="AL7" s="3"/>
-    </row>
-    <row r="8" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM7" s="3"/>
+      <c r="AN7" s="3"/>
+    </row>
+    <row r="8" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E8" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N8" s="3">
         <v>20</v>
       </c>
       <c r="O8" s="3"/>
       <c r="P8" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q8" s="3">
         <v>1</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T8" s="3"/>
       <c r="U8" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
@@ -1459,54 +1526,56 @@
       <c r="AJ8" s="3"/>
       <c r="AK8" s="3"/>
       <c r="AL8" s="3"/>
-    </row>
-    <row r="9" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM8" s="3"/>
+      <c r="AN8" s="3"/>
+    </row>
+    <row r="9" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E9" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N9" s="3">
         <v>17</v>
       </c>
       <c r="O9" s="3"/>
       <c r="P9" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q9" s="3">
         <v>1</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
@@ -1517,66 +1586,64 @@
       <c r="AB9" s="3"/>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
-      <c r="AE9" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="AF9" s="3" t="s">
-        <v>126</v>
-      </c>
+      <c r="AE9" s="3"/>
+      <c r="AF9" s="3"/>
       <c r="AG9" s="3"/>
       <c r="AH9" s="3"/>
       <c r="AI9" s="3"/>
       <c r="AJ9" s="3"/>
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
-    </row>
-    <row r="10" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM9" s="3"/>
+      <c r="AN9" s="3"/>
+    </row>
+    <row r="10" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E10" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N10" s="3">
         <v>1.3</v>
       </c>
       <c r="O10" s="3"/>
       <c r="P10" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q10" s="3">
         <v>1</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
@@ -1595,54 +1662,56 @@
       <c r="AJ10" s="3"/>
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
-    </row>
-    <row r="11" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM10" s="3"/>
+      <c r="AN10" s="3"/>
+    </row>
+    <row r="11" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E11" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N11" s="3">
         <v>0.3</v>
       </c>
       <c r="O11" s="3"/>
       <c r="P11" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q11" s="3">
         <v>1</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T11" s="3"/>
       <c r="U11" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
@@ -1661,52 +1730,54 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
-    </row>
-    <row r="12" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+    </row>
+    <row r="12" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E12" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N12" s="3">
         <v>110</v>
       </c>
       <c r="O12" s="3"/>
       <c r="P12" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q12" s="3">
         <v>1</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T12" s="3"/>
       <c r="U12" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
@@ -1725,52 +1796,54 @@
       <c r="AJ12" s="3"/>
       <c r="AK12" s="3"/>
       <c r="AL12" s="3"/>
-    </row>
-    <row r="13" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM12" s="3"/>
+      <c r="AN12" s="3"/>
+    </row>
+    <row r="13" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E13" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N13" s="3">
         <v>750</v>
       </c>
       <c r="O13" s="3"/>
       <c r="P13" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q13" s="3">
         <v>1</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T13" s="3"/>
       <c r="U13" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
@@ -1789,52 +1862,54 @@
       <c r="AJ13" s="3"/>
       <c r="AK13" s="3"/>
       <c r="AL13" s="3"/>
-    </row>
-    <row r="14" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM13" s="3"/>
+      <c r="AN13" s="3"/>
+    </row>
+    <row r="14" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E14" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N14" s="3">
         <v>300</v>
       </c>
       <c r="O14" s="3"/>
       <c r="P14" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q14" s="3">
         <v>1</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T14" s="3"/>
       <c r="U14" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
@@ -1853,52 +1928,54 @@
       <c r="AJ14" s="3"/>
       <c r="AK14" s="3"/>
       <c r="AL14" s="3"/>
-    </row>
-    <row r="15" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM14" s="3"/>
+      <c r="AN14" s="3"/>
+    </row>
+    <row r="15" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N15" s="3">
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="O15" s="3"/>
       <c r="P15" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q15" s="3">
         <v>1</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T15" s="3"/>
       <c r="U15" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
@@ -1917,52 +1994,54 @@
       <c r="AJ15" s="3"/>
       <c r="AK15" s="3"/>
       <c r="AL15" s="3"/>
-    </row>
-    <row r="16" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM15" s="3"/>
+      <c r="AN15" s="3"/>
+    </row>
+    <row r="16" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N16" s="3">
         <v>1000</v>
       </c>
       <c r="O16" s="3"/>
       <c r="P16" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q16" s="3">
         <v>1</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
@@ -1981,52 +2060,54 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
-    </row>
-    <row r="17" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
+    </row>
+    <row r="17" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N17" s="3">
         <v>5</v>
       </c>
       <c r="O17" s="3"/>
       <c r="P17" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q17" s="3">
         <v>1</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T17" s="3"/>
       <c r="U17" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
@@ -2045,52 +2126,54 @@
       <c r="AJ17" s="3"/>
       <c r="AK17" s="3"/>
       <c r="AL17" s="3"/>
-    </row>
-    <row r="18" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM17" s="3"/>
+      <c r="AN17" s="3"/>
+    </row>
+    <row r="18" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N18" s="3">
         <v>1300</v>
       </c>
       <c r="O18" s="3"/>
       <c r="P18" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q18" s="3">
         <v>1</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T18" s="3"/>
       <c r="U18" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
@@ -2109,52 +2192,54 @@
       <c r="AJ18" s="3"/>
       <c r="AK18" s="3"/>
       <c r="AL18" s="3"/>
-    </row>
-    <row r="19" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM18" s="3"/>
+      <c r="AN18" s="3"/>
+    </row>
+    <row r="19" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N19" s="3">
         <v>4000</v>
       </c>
       <c r="O19" s="3"/>
       <c r="P19" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q19" s="3">
         <v>1</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T19" s="3"/>
       <c r="U19" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
@@ -2173,52 +2258,54 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
-    </row>
-    <row r="20" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
+    </row>
+    <row r="20" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N20" s="3">
         <v>300</v>
       </c>
       <c r="O20" s="3"/>
       <c r="P20" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q20" s="3">
         <v>1</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T20" s="3"/>
       <c r="U20" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
@@ -2237,52 +2324,54 @@
       <c r="AJ20" s="3"/>
       <c r="AK20" s="3"/>
       <c r="AL20" s="3"/>
-    </row>
-    <row r="21" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM20" s="3"/>
+      <c r="AN20" s="3"/>
+    </row>
+    <row r="21" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N21" s="3">
         <v>15</v>
       </c>
       <c r="O21" s="3"/>
       <c r="P21" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q21" s="3">
         <v>1</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T21" s="3"/>
       <c r="U21" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
@@ -2301,52 +2390,54 @@
       <c r="AJ21" s="3"/>
       <c r="AK21" s="3"/>
       <c r="AL21" s="3"/>
-    </row>
-    <row r="22" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM21" s="3"/>
+      <c r="AN21" s="3"/>
+    </row>
+    <row r="22" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N22" s="3">
         <v>610</v>
       </c>
       <c r="O22" s="3"/>
       <c r="P22" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q22" s="3">
         <v>1</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T22" s="3"/>
       <c r="U22" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
@@ -2365,52 +2456,54 @@
       <c r="AJ22" s="3"/>
       <c r="AK22" s="3"/>
       <c r="AL22" s="3"/>
-    </row>
-    <row r="23" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM22" s="3"/>
+      <c r="AN22" s="3"/>
+    </row>
+    <row r="23" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N23" s="3">
         <v>50</v>
       </c>
       <c r="O23" s="3"/>
       <c r="P23" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q23" s="3">
         <v>1</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T23" s="3"/>
       <c r="U23" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
@@ -2429,54 +2522,56 @@
       <c r="AJ23" s="3"/>
       <c r="AK23" s="3"/>
       <c r="AL23" s="3"/>
-    </row>
-    <row r="24" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM23" s="3"/>
+      <c r="AN23" s="3"/>
+    </row>
+    <row r="24" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N24" s="3">
         <v>7400</v>
       </c>
       <c r="O24" s="3"/>
       <c r="P24" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q24" s="3">
         <v>1</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T24" s="3">
         <v>1</v>
       </c>
       <c r="U24" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
@@ -2495,68 +2590,70 @@
       <c r="AJ24" s="3"/>
       <c r="AK24" s="3"/>
       <c r="AL24" s="3"/>
-    </row>
-    <row r="25" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM24" s="3"/>
+      <c r="AN24" s="3"/>
+    </row>
+    <row r="25" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N25" s="3">
         <v>235</v>
       </c>
       <c r="O25" s="3"/>
       <c r="P25" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Q25" s="3">
         <v>1</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T25" s="3">
         <v>1</v>
       </c>
       <c r="U25" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="Z25" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AA25" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AB25" s="3"/>
       <c r="AC25" s="3"/>
@@ -2569,68 +2666,70 @@
       <c r="AJ25" s="3"/>
       <c r="AK25" s="3"/>
       <c r="AL25" s="3"/>
-    </row>
-    <row r="26" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM25" s="3"/>
+      <c r="AN25" s="3"/>
+    </row>
+    <row r="26" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E26" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N26" s="3">
         <v>235</v>
       </c>
       <c r="O26" s="3"/>
       <c r="P26" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Q26" s="3">
         <v>1</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T26" s="3">
         <v>1</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
       <c r="Y26" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="Z26" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AA26" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AB26" s="3"/>
       <c r="AC26" s="3"/>
@@ -2643,66 +2742,68 @@
       <c r="AJ26" s="3"/>
       <c r="AK26" s="3"/>
       <c r="AL26" s="3"/>
-    </row>
-    <row r="27" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM26" s="3"/>
+      <c r="AN26" s="3"/>
+    </row>
+    <row r="27" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N27" s="3">
         <v>126</v>
       </c>
       <c r="O27" s="3"/>
       <c r="P27" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Q27" s="3">
         <v>1</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T27" s="3">
         <v>1</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
       <c r="Y27" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="Z27" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AA27" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AB27" s="3"/>
       <c r="AC27" s="3"/>
@@ -2715,66 +2816,68 @@
       <c r="AJ27" s="3"/>
       <c r="AK27" s="3"/>
       <c r="AL27" s="3"/>
-    </row>
-    <row r="28" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM27" s="3"/>
+      <c r="AN27" s="3"/>
+    </row>
+    <row r="28" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E28" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N28" s="3">
         <v>126</v>
       </c>
       <c r="O28" s="3"/>
       <c r="P28" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Q28" s="3">
         <v>1</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T28" s="3">
         <v>1</v>
       </c>
       <c r="U28" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="Z28" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AA28" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AB28" s="3"/>
       <c r="AC28" s="3"/>
@@ -2787,66 +2890,68 @@
       <c r="AJ28" s="3"/>
       <c r="AK28" s="3"/>
       <c r="AL28" s="3"/>
-    </row>
-    <row r="29" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM28" s="3"/>
+      <c r="AN28" s="3"/>
+    </row>
+    <row r="29" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N29" s="3">
         <v>126</v>
       </c>
       <c r="O29" s="3"/>
       <c r="P29" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Q29" s="3">
         <v>1</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T29" s="3">
         <v>1</v>
       </c>
       <c r="U29" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
       <c r="Y29" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="Z29" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AA29" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AB29" s="3"/>
       <c r="AC29" s="3"/>
@@ -2859,58 +2964,60 @@
       <c r="AJ29" s="3"/>
       <c r="AK29" s="3"/>
       <c r="AL29" s="3"/>
-    </row>
-    <row r="30" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM29" s="3"/>
+      <c r="AN29" s="3"/>
+    </row>
+    <row r="30" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E30" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N30" s="3">
         <v>6.5</v>
       </c>
       <c r="O30" s="3"/>
       <c r="P30" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q30" s="3">
         <v>30</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T30" s="3">
         <v>1</v>
       </c>
       <c r="U30" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
@@ -2929,58 +3036,60 @@
       <c r="AJ30" s="3"/>
       <c r="AK30" s="3"/>
       <c r="AL30" s="3"/>
-    </row>
-    <row r="31" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM30" s="3"/>
+      <c r="AN30" s="3"/>
+    </row>
+    <row r="31" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E31" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N31" s="3">
         <v>5.5</v>
       </c>
       <c r="O31" s="3"/>
       <c r="P31" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q31" s="3">
         <v>30</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T31" s="3">
         <v>1</v>
       </c>
       <c r="U31" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
@@ -2999,58 +3108,60 @@
       <c r="AJ31" s="3"/>
       <c r="AK31" s="3"/>
       <c r="AL31" s="3"/>
-    </row>
-    <row r="32" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM31" s="3"/>
+      <c r="AN31" s="3"/>
+    </row>
+    <row r="32" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E32" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N32" s="3">
         <v>9.5</v>
       </c>
       <c r="O32" s="3"/>
       <c r="P32" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q32" s="3">
         <v>7</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S32" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T32" s="3">
         <v>1</v>
       </c>
       <c r="U32" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
@@ -3069,58 +3180,60 @@
       <c r="AJ32" s="3"/>
       <c r="AK32" s="3"/>
       <c r="AL32" s="3"/>
-    </row>
-    <row r="33" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM32" s="3"/>
+      <c r="AN32" s="3"/>
+    </row>
+    <row r="33" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E33" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N33" s="3">
         <v>6</v>
       </c>
       <c r="O33" s="3"/>
       <c r="P33" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q33" s="3">
         <v>7</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S33" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T33" s="3">
         <v>1</v>
       </c>
       <c r="U33" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
@@ -3139,58 +3252,60 @@
       <c r="AJ33" s="3"/>
       <c r="AK33" s="3"/>
       <c r="AL33" s="3"/>
-    </row>
-    <row r="34" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM33" s="3"/>
+      <c r="AN33" s="3"/>
+    </row>
+    <row r="34" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E34" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N34" s="3">
         <v>8</v>
       </c>
       <c r="O34" s="3"/>
       <c r="P34" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q34" s="3">
         <v>1</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S34" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="T34" s="3">
         <v>1</v>
       </c>
       <c r="U34" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
@@ -3209,58 +3324,60 @@
       <c r="AJ34" s="3"/>
       <c r="AK34" s="3"/>
       <c r="AL34" s="3"/>
-    </row>
-    <row r="35" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM34" s="3"/>
+      <c r="AN34" s="3"/>
+    </row>
+    <row r="35" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E35" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N35" s="3">
         <v>4</v>
       </c>
       <c r="O35" s="3"/>
       <c r="P35" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q35" s="3">
         <v>1</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S35" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="T35" s="3">
         <v>1</v>
       </c>
       <c r="U35" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
@@ -3279,58 +3396,60 @@
       <c r="AJ35" s="3"/>
       <c r="AK35" s="3"/>
       <c r="AL35" s="3"/>
-    </row>
-    <row r="36" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM35" s="3"/>
+      <c r="AN35" s="3"/>
+    </row>
+    <row r="36" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E36" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N36" s="3">
         <v>5</v>
       </c>
       <c r="O36" s="3"/>
       <c r="P36" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q36" s="3">
         <v>1</v>
       </c>
       <c r="R36" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S36" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="T36" s="3">
         <v>1</v>
       </c>
       <c r="U36" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
@@ -3349,58 +3468,60 @@
       <c r="AJ36" s="3"/>
       <c r="AK36" s="3"/>
       <c r="AL36" s="3"/>
-    </row>
-    <row r="37" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM36" s="3"/>
+      <c r="AN36" s="3"/>
+    </row>
+    <row r="37" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E37" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N37" s="3">
         <v>3</v>
       </c>
       <c r="O37" s="3"/>
       <c r="P37" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q37" s="3">
         <v>1</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="T37" s="3">
         <v>1</v>
       </c>
       <c r="U37" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
@@ -3419,58 +3540,60 @@
       <c r="AJ37" s="3"/>
       <c r="AK37" s="3"/>
       <c r="AL37" s="3"/>
-    </row>
-    <row r="38" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM37" s="3"/>
+      <c r="AN37" s="3"/>
+    </row>
+    <row r="38" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E38" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N38" s="3">
         <v>5</v>
       </c>
       <c r="O38" s="3"/>
       <c r="P38" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q38" s="3">
         <v>7</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="T38" s="3">
         <v>1</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
@@ -3489,58 +3612,60 @@
       <c r="AJ38" s="3"/>
       <c r="AK38" s="3"/>
       <c r="AL38" s="3"/>
-    </row>
-    <row r="39" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM38" s="3"/>
+      <c r="AN38" s="3"/>
+    </row>
+    <row r="39" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E39" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N39" s="3">
         <v>4</v>
       </c>
       <c r="O39" s="3"/>
       <c r="P39" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q39" s="3">
         <v>7</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="T39" s="3">
         <v>1</v>
       </c>
       <c r="U39" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
@@ -3559,56 +3684,58 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
-    </row>
-    <row r="40" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
+    </row>
+    <row r="40" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E40" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q40" s="3">
         <v>1</v>
       </c>
       <c r="R40" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S40" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T40" s="3">
         <v>1</v>
       </c>
       <c r="U40" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
@@ -3620,73 +3747,74 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AF40" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-      <c r="AI40" s="3">
-        <v>1</v>
-      </c>
+      <c r="AI40" s="3"/>
       <c r="AJ40" s="3">
+        <v>1</v>
+      </c>
+      <c r="AK40" s="3">
         <v>0.97889999999999999</v>
       </c>
-      <c r="AK40" s="3">
+      <c r="AL40" s="3">
         <v>-3.8660000000000001</v>
       </c>
-      <c r="AL40" s="3"/>
-    </row>
-    <row r="41" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AN40" s="3"/>
+    </row>
+    <row r="41" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E41" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="N41" s="3"/>
       <c r="O41" s="3"/>
       <c r="P41" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q41" s="3">
         <v>30</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S41" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T41" s="3">
         <v>1</v>
       </c>
       <c r="U41" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
@@ -3698,73 +3826,74 @@
       <c r="AC41" s="3"/>
       <c r="AD41" s="3"/>
       <c r="AE41" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AF41" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG41" s="3"/>
       <c r="AH41" s="3"/>
-      <c r="AI41" s="3">
-        <v>1</v>
-      </c>
+      <c r="AI41" s="3"/>
       <c r="AJ41" s="3">
+        <v>1</v>
+      </c>
+      <c r="AK41" s="3">
         <v>0.79769999999999996</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>-3.9089999999999998</v>
       </c>
-      <c r="AL41" s="3"/>
-    </row>
-    <row r="42" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AN41" s="3"/>
+    </row>
+    <row r="42" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E42" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="N42" s="3"/>
       <c r="O42" s="3"/>
       <c r="P42" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q42" s="3">
         <v>1</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S42" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T42" s="3">
         <v>1</v>
       </c>
       <c r="U42" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
@@ -3776,73 +3905,74 @@
       <c r="AC42" s="3"/>
       <c r="AD42" s="3"/>
       <c r="AE42" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AF42" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AG42" s="3"/>
       <c r="AH42" s="3"/>
-      <c r="AI42" s="3">
-        <v>1</v>
-      </c>
+      <c r="AI42" s="3"/>
       <c r="AJ42" s="3">
+        <v>1</v>
+      </c>
+      <c r="AK42" s="3">
         <v>0.81899999999999995</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>3.7256</v>
       </c>
-      <c r="AL42" s="3"/>
-    </row>
-    <row r="43" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AN42" s="3"/>
+    </row>
+    <row r="43" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E43" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="N43" s="3"/>
       <c r="O43" s="3"/>
       <c r="P43" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q43" s="3">
         <v>30</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S43" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T43" s="3">
         <v>1</v>
       </c>
       <c r="U43" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3"/>
@@ -3854,73 +3984,74 @@
       <c r="AC43" s="3"/>
       <c r="AD43" s="3"/>
       <c r="AE43" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AF43" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AG43" s="3"/>
       <c r="AH43" s="3"/>
-      <c r="AI43" s="3">
-        <v>1</v>
-      </c>
+      <c r="AI43" s="3"/>
       <c r="AJ43" s="3">
+        <v>1</v>
+      </c>
+      <c r="AK43" s="3">
         <v>0.81899999999999995</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>0.68479999999999996</v>
       </c>
-      <c r="AL43" s="3"/>
-    </row>
-    <row r="44" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AN43" s="3"/>
+    </row>
+    <row r="44" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E44" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G44" s="3"/>
       <c r="H44" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I44" s="3"/>
       <c r="J44" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="N44" s="3"/>
       <c r="O44" s="3"/>
       <c r="P44" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q44" s="3">
         <v>1</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S44" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T44" s="3">
         <v>1</v>
       </c>
       <c r="U44" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
@@ -3932,73 +4063,74 @@
       <c r="AC44" s="3"/>
       <c r="AD44" s="3"/>
       <c r="AE44" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AF44" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AG44" s="3"/>
       <c r="AH44" s="3"/>
-      <c r="AI44" s="3">
-        <v>1</v>
-      </c>
+      <c r="AI44" s="3"/>
       <c r="AJ44" s="3">
+        <v>1</v>
+      </c>
+      <c r="AK44" s="3">
         <v>1.2729999999999999</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>-1.46</v>
       </c>
-      <c r="AL44" s="3"/>
-    </row>
-    <row r="45" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AN44" s="3"/>
+    </row>
+    <row r="45" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E45" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q45" s="3">
         <v>30</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S45" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T45" s="3">
         <v>1</v>
       </c>
       <c r="U45" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V45" s="3"/>
       <c r="W45" s="3"/>
@@ -4010,73 +4142,74 @@
       <c r="AC45" s="3"/>
       <c r="AD45" s="3"/>
       <c r="AE45" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AF45" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AG45" s="3"/>
       <c r="AH45" s="3"/>
-      <c r="AI45" s="3">
-        <v>1</v>
-      </c>
+      <c r="AI45" s="3"/>
       <c r="AJ45" s="3">
+        <v>1</v>
+      </c>
+      <c r="AK45" s="3">
         <v>1.2729999999999999</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>-4.7050000000000001</v>
       </c>
-      <c r="AL45" s="3"/>
-    </row>
-    <row r="46" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AN45" s="3"/>
+    </row>
+    <row r="46" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E46" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
       <c r="P46" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q46" s="3">
         <v>1</v>
       </c>
       <c r="R46" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S46" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T46" s="3">
         <v>1</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
@@ -4088,73 +4221,74 @@
       <c r="AC46" s="3"/>
       <c r="AD46" s="3"/>
       <c r="AE46" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AF46" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AG46" s="3"/>
       <c r="AH46" s="3"/>
-      <c r="AI46" s="3">
-        <v>1</v>
-      </c>
+      <c r="AI46" s="3"/>
       <c r="AJ46" s="3">
+        <v>1</v>
+      </c>
+      <c r="AK46" s="3">
         <v>0.84599999999999997</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2.2549999999999999</v>
       </c>
-      <c r="AL46" s="3"/>
-    </row>
-    <row r="47" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AN46" s="3"/>
+    </row>
+    <row r="47" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E47" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
       <c r="P47" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q47" s="3">
         <v>30</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S47" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T47" s="3">
         <v>1</v>
       </c>
       <c r="U47" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
@@ -4166,73 +4300,74 @@
       <c r="AC47" s="3"/>
       <c r="AD47" s="3"/>
       <c r="AE47" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AF47" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AG47" s="3"/>
       <c r="AH47" s="3"/>
-      <c r="AI47" s="3">
-        <v>1</v>
-      </c>
+      <c r="AI47" s="3"/>
       <c r="AJ47" s="3">
+        <v>1</v>
+      </c>
+      <c r="AK47" s="3">
         <v>0.84599999999999997</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>5.8400000000000001E-2</v>
       </c>
-      <c r="AL47" s="3"/>
-    </row>
-    <row r="48" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AN47" s="3"/>
+    </row>
+    <row r="48" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E48" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I48" s="3"/>
       <c r="J48" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
       <c r="P48" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q48" s="3">
         <v>1</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T48" s="3">
         <v>1</v>
       </c>
       <c r="U48" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
@@ -4244,73 +4379,74 @@
       <c r="AC48" s="3"/>
       <c r="AD48" s="3"/>
       <c r="AE48" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AF48" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AG48" s="3"/>
       <c r="AH48" s="3"/>
-      <c r="AI48" s="3">
-        <v>1</v>
-      </c>
+      <c r="AI48" s="3"/>
       <c r="AJ48" s="3">
+        <v>1</v>
+      </c>
+      <c r="AK48" s="3">
         <v>1.72</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>-6.59</v>
       </c>
-      <c r="AL48" s="3"/>
-    </row>
-    <row r="49" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AN48" s="3"/>
+    </row>
+    <row r="49" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E49" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I49" s="3"/>
       <c r="J49" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="N49" s="3"/>
       <c r="O49" s="3"/>
       <c r="P49" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q49" s="3">
         <v>1</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S49" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T49" s="3">
         <v>1</v>
       </c>
       <c r="U49" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="3"/>
@@ -4322,73 +4458,74 @@
       <c r="AC49" s="3"/>
       <c r="AD49" s="3"/>
       <c r="AE49" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AF49" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="AG49" s="3"/>
       <c r="AH49" s="3"/>
-      <c r="AI49" s="3">
-        <v>1</v>
-      </c>
+      <c r="AI49" s="3"/>
       <c r="AJ49" s="3">
+        <v>1</v>
+      </c>
+      <c r="AK49" s="3">
         <v>0.84730000000000005</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>0.88400000000000001</v>
       </c>
-      <c r="AL49" s="3"/>
-    </row>
-    <row r="50" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AN49" s="3"/>
+    </row>
+    <row r="50" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E50" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I50" s="3"/>
       <c r="J50" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="3"/>
       <c r="P50" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q50" s="3">
         <v>30</v>
       </c>
       <c r="R50" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S50" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T50" s="3">
         <v>1</v>
       </c>
       <c r="U50" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
@@ -4400,26 +4537,27 @@
       <c r="AC50" s="3"/>
       <c r="AD50" s="3"/>
       <c r="AE50" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AF50" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="AG50" s="3"/>
       <c r="AH50" s="3"/>
-      <c r="AI50" s="3">
-        <v>1</v>
-      </c>
+      <c r="AI50" s="3"/>
       <c r="AJ50" s="3">
+        <v>1</v>
+      </c>
+      <c r="AK50" s="3">
         <v>0.84730000000000005</v>
       </c>
-      <c r="AK50" s="3">
+      <c r="AL50" s="3">
         <v>0.88400000000000001</v>
       </c>
-      <c r="AL50" s="3"/>
+      <c r="AN50" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP50" xr:uid="{48473D4D-2A67-413E-80AF-8677973F00EA}"/>
+  <autoFilter ref="A1:AR50" xr:uid="{48473D4D-2A67-413E-80AF-8677973F00EA}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/inst/extdata/fort_peck_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/fort_peck_tribe_criteria_crosswalk.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/hannah_ferriby_tetratech_com/Documents/Documents/GitHub/TADACommunityHub/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{F4F0DC3D-5790-4B74-910A-1FBDBD12360F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{283FD004-495A-4A47-9967-A5E4A4E01251}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{F4F0DC3D-5790-4B74-910A-1FBDBD12360F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BC8C9CF-0155-4B82-8D02-D793B1EA3FB4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A9D2C00B-42FB-4D75-83D9-FF6DA97293BD}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="143">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -437,9 +437,6 @@
     <t>pHDirection</t>
   </si>
   <si>
-    <t>TemperatureExtreme</t>
-  </si>
-  <si>
     <t>pH_param_5</t>
   </si>
   <si>
@@ -459,6 +456,18 @@
   </si>
   <si>
     <t>MaxEqMagnitude</t>
+  </si>
+  <si>
+    <t>AmmoniaEqType</t>
+  </si>
+  <si>
+    <t>pH_param_10</t>
+  </si>
+  <si>
+    <t>pH_param_11</t>
+  </si>
+  <si>
+    <t>pH_param_12</t>
   </si>
 </sst>
 </file>
@@ -880,7 +889,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48473D4D-2A67-413E-80AF-8677973F00EA}">
-  <dimension ref="A1:AX50"/>
+  <dimension ref="A1:BA50"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="5"/>
@@ -897,7 +906,7 @@
     <col min="28" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:53" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1013,7 +1022,7 @@
         <v>34</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="AN1" s="1" t="s">
         <v>35</v>
@@ -1028,28 +1037,37 @@
         <v>38</v>
       </c>
       <c r="AR1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="AS1" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="AZ1" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="AW1" s="6" t="s">
+      <c r="BA1" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="AX1" s="6" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="2" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
         <v>39</v>
@@ -1119,7 +1137,7 @@
       <c r="AM2" s="3"/>
       <c r="AN2" s="3"/>
     </row>
-    <row r="3" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
         <v>39</v>
@@ -1189,7 +1207,7 @@
       <c r="AM3" s="3"/>
       <c r="AN3" s="3"/>
     </row>
-    <row r="4" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
         <v>39</v>
@@ -1257,7 +1275,7 @@
       <c r="AM4" s="3"/>
       <c r="AN4" s="3"/>
     </row>
-    <row r="5" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
         <v>39</v>
@@ -1325,7 +1343,7 @@
       <c r="AM5" s="3"/>
       <c r="AN5" s="3"/>
     </row>
-    <row r="6" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
         <v>39</v>
@@ -1393,7 +1411,7 @@
       <c r="AM6" s="3"/>
       <c r="AN6" s="3"/>
     </row>
-    <row r="7" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
         <v>39</v>
@@ -1461,7 +1479,7 @@
       <c r="AM7" s="3"/>
       <c r="AN7" s="3"/>
     </row>
-    <row r="8" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
         <v>39</v>
@@ -1529,7 +1547,7 @@
       <c r="AM8" s="3"/>
       <c r="AN8" s="3"/>
     </row>
-    <row r="9" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
         <v>39</v>
@@ -1597,7 +1615,7 @@
       <c r="AM9" s="3"/>
       <c r="AN9" s="3"/>
     </row>
-    <row r="10" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
         <v>39</v>
@@ -1665,7 +1683,7 @@
       <c r="AM10" s="3"/>
       <c r="AN10" s="3"/>
     </row>
-    <row r="11" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
         <v>39</v>
@@ -1733,7 +1751,7 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
         <v>39</v>
@@ -1799,7 +1817,7 @@
       <c r="AM12" s="3"/>
       <c r="AN12" s="3"/>
     </row>
-    <row r="13" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
         <v>39</v>
@@ -1865,7 +1883,7 @@
       <c r="AM13" s="3"/>
       <c r="AN13" s="3"/>
     </row>
-    <row r="14" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
         <v>39</v>
@@ -1931,7 +1949,7 @@
       <c r="AM14" s="3"/>
       <c r="AN14" s="3"/>
     </row>
-    <row r="15" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
         <v>39</v>
@@ -1997,7 +2015,7 @@
       <c r="AM15" s="3"/>
       <c r="AN15" s="3"/>
     </row>
-    <row r="16" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
         <v>39</v>

--- a/inst/extdata/fort_peck_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/fort_peck_tribe_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/hannah_ferriby_tetratech_com/Documents/Documents/GitHub/TADACommunityHub/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{F4F0DC3D-5790-4B74-910A-1FBDBD12360F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BC8C9CF-0155-4B82-8D02-D793B1EA3FB4}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{F4F0DC3D-5790-4B74-910A-1FBDBD12360F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{216EC135-44A4-4679-8628-7FFB3E16B8BF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A9D2C00B-42FB-4D75-83D9-FF6DA97293BD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A9D2C00B-42FB-4D75-83D9-FF6DA97293BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="142">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -104,18 +104,12 @@
     <t>FreqMethod</t>
   </si>
   <si>
-    <t>AssessPeriod</t>
-  </si>
-  <si>
     <t>AssessPeriodStartDate</t>
   </si>
   <si>
     <t>AssessPeriodEndDate</t>
   </si>
   <si>
-    <t>Season</t>
-  </si>
-  <si>
     <t>SeasonStartDate</t>
   </si>
   <si>
@@ -422,9 +416,6 @@
     <t>Sep 30</t>
   </si>
   <si>
-    <t>Jun-Sep</t>
-  </si>
-  <si>
     <t>CFU/100ML</t>
   </si>
   <si>
@@ -468,6 +459,12 @@
   </si>
   <si>
     <t>pH_param_12</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Links</t>
   </si>
 </sst>
 </file>
@@ -890,23 +887,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48473D4D-2A67-413E-80AF-8677973F00EA}">
   <dimension ref="A1:BA50"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="9.140625" style="5"/>
+    <col min="1" max="2" width="9.109375" style="5"/>
     <col min="3" max="3" width="27" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.140625" style="5" customWidth="1"/>
-    <col min="6" max="17" width="9.140625" style="5"/>
-    <col min="18" max="18" width="15.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="20" max="24" width="9.140625" style="5"/>
-    <col min="25" max="25" width="16.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.140625" style="5"/>
-    <col min="27" max="27" width="10.7109375" style="5" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="5"/>
+    <col min="4" max="4" width="20.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.109375" style="5" customWidth="1"/>
+    <col min="6" max="17" width="9.109375" style="5"/>
+    <col min="18" max="18" width="15.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="20" max="24" width="9.109375" style="5"/>
+    <col min="25" max="25" width="10.6640625" style="5" customWidth="1"/>
+    <col min="26" max="16384" width="9.109375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:53" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -992,108 +987,108 @@
         <v>27</v>
       </c>
       <c r="AC1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="AE1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AK1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR1" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="AI1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AK1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AL1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AY1" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="AN1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AZ1" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="BA1" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="AV1" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="AZ1" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="BA1" s="6" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="2" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K2" s="3"/>
       <c r="L2" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N2" s="3">
         <v>6.5</v>
@@ -1102,27 +1097,27 @@
         <v>9</v>
       </c>
       <c r="P2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>1</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S2" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>1</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="T2" s="3"/>
       <c r="U2" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
       <c r="AB2" s="3"/>
       <c r="AC2" s="3"/>
       <c r="AD2" s="3"/>
@@ -1137,33 +1132,33 @@
       <c r="AM2" s="3"/>
       <c r="AN2" s="3"/>
     </row>
-    <row r="3" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N3" s="3">
         <v>6.5</v>
@@ -1172,27 +1167,27 @@
         <v>9</v>
       </c>
       <c r="P3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>1</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S3" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="Q3" s="3">
-        <v>1</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="T3" s="3"/>
       <c r="U3" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="4"/>
-      <c r="AA3" s="4"/>
+      <c r="X3" s="4"/>
+      <c r="Y3" s="4"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
       <c r="AB3" s="3"/>
       <c r="AC3" s="3"/>
       <c r="AD3" s="3"/>
@@ -1207,60 +1202,60 @@
       <c r="AM3" s="3"/>
       <c r="AN3" s="3"/>
     </row>
-    <row r="4" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E4" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N4" s="3">
         <v>27</v>
       </c>
       <c r="O4" s="3"/>
       <c r="P4" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="Q4" s="3">
         <v>1</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="4"/>
-      <c r="AA4" s="4"/>
+      <c r="X4" s="4"/>
+      <c r="Y4" s="4"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
       <c r="AB4" s="3"/>
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
@@ -1275,60 +1270,60 @@
       <c r="AM4" s="3"/>
       <c r="AN4" s="3"/>
     </row>
-    <row r="5" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E5" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N5" s="3">
         <v>23</v>
       </c>
       <c r="O5" s="3"/>
       <c r="P5" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="Q5" s="3">
         <v>1</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T5" s="3"/>
       <c r="U5" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="4"/>
-      <c r="AA5" s="4"/>
+      <c r="X5" s="4"/>
+      <c r="Y5" s="4"/>
+      <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
       <c r="AB5" s="3"/>
       <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
@@ -1343,60 +1338,60 @@
       <c r="AM5" s="3"/>
       <c r="AN5" s="3"/>
     </row>
-    <row r="6" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E6" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N6" s="3">
         <v>860000</v>
       </c>
       <c r="O6" s="3"/>
       <c r="P6" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Q6" s="3">
         <v>1</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T6" s="3"/>
       <c r="U6" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="4"/>
-      <c r="AA6" s="4"/>
+      <c r="X6" s="4"/>
+      <c r="Y6" s="4"/>
+      <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
       <c r="AB6" s="3"/>
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
@@ -1411,60 +1406,60 @@
       <c r="AM6" s="3"/>
       <c r="AN6" s="3"/>
     </row>
-    <row r="7" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E7" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N7" s="3">
         <v>230000</v>
       </c>
       <c r="O7" s="3"/>
       <c r="P7" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Q7" s="3">
         <v>1</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T7" s="3"/>
       <c r="U7" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="4"/>
-      <c r="AA7" s="4"/>
+      <c r="X7" s="4"/>
+      <c r="Y7" s="4"/>
+      <c r="Z7" s="3"/>
+      <c r="AA7" s="3"/>
       <c r="AB7" s="3"/>
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
@@ -1479,60 +1474,60 @@
       <c r="AM7" s="3"/>
       <c r="AN7" s="3"/>
     </row>
-    <row r="8" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E8" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N8" s="3">
         <v>20</v>
       </c>
       <c r="O8" s="3"/>
       <c r="P8" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q8" s="3">
         <v>1</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T8" s="3"/>
       <c r="U8" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="4"/>
-      <c r="AA8" s="4"/>
+      <c r="X8" s="4"/>
+      <c r="Y8" s="4"/>
+      <c r="Z8" s="3"/>
+      <c r="AA8" s="3"/>
       <c r="AB8" s="3"/>
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
@@ -1547,60 +1542,60 @@
       <c r="AM8" s="3"/>
       <c r="AN8" s="3"/>
     </row>
-    <row r="9" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E9" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N9" s="3">
         <v>17</v>
       </c>
       <c r="O9" s="3"/>
       <c r="P9" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q9" s="3">
         <v>1</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="4"/>
-      <c r="AA9" s="4"/>
+      <c r="X9" s="4"/>
+      <c r="Y9" s="4"/>
+      <c r="Z9" s="3"/>
+      <c r="AA9" s="3"/>
       <c r="AB9" s="3"/>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
@@ -1615,60 +1610,60 @@
       <c r="AM9" s="3"/>
       <c r="AN9" s="3"/>
     </row>
-    <row r="10" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E10" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N10" s="3">
         <v>1.3</v>
       </c>
       <c r="O10" s="3"/>
       <c r="P10" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q10" s="3">
         <v>1</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="4"/>
-      <c r="AA10" s="4"/>
+      <c r="X10" s="4"/>
+      <c r="Y10" s="4"/>
+      <c r="Z10" s="3"/>
+      <c r="AA10" s="3"/>
       <c r="AB10" s="3"/>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
@@ -1683,60 +1678,60 @@
       <c r="AM10" s="3"/>
       <c r="AN10" s="3"/>
     </row>
-    <row r="11" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E11" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N11" s="3">
         <v>0.3</v>
       </c>
       <c r="O11" s="3"/>
       <c r="P11" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q11" s="3">
         <v>1</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T11" s="3"/>
       <c r="U11" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="4"/>
-      <c r="AA11" s="4"/>
+      <c r="X11" s="4"/>
+      <c r="Y11" s="4"/>
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
@@ -1751,58 +1746,58 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E12" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N12" s="3">
         <v>110</v>
       </c>
       <c r="O12" s="3"/>
       <c r="P12" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Q12" s="3">
         <v>1</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T12" s="3"/>
       <c r="U12" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="4"/>
-      <c r="AA12" s="4"/>
+      <c r="X12" s="4"/>
+      <c r="Y12" s="4"/>
+      <c r="Z12" s="3"/>
+      <c r="AA12" s="3"/>
       <c r="AB12" s="3"/>
       <c r="AC12" s="3"/>
       <c r="AD12" s="3"/>
@@ -1817,58 +1812,58 @@
       <c r="AM12" s="3"/>
       <c r="AN12" s="3"/>
     </row>
-    <row r="13" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E13" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N13" s="3">
         <v>750</v>
       </c>
       <c r="O13" s="3"/>
       <c r="P13" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Q13" s="3">
         <v>1</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T13" s="3"/>
       <c r="U13" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="4"/>
-      <c r="AA13" s="4"/>
+      <c r="X13" s="4"/>
+      <c r="Y13" s="4"/>
+      <c r="Z13" s="3"/>
+      <c r="AA13" s="3"/>
       <c r="AB13" s="3"/>
       <c r="AC13" s="3"/>
       <c r="AD13" s="3"/>
@@ -1883,58 +1878,58 @@
       <c r="AM13" s="3"/>
       <c r="AN13" s="3"/>
     </row>
-    <row r="14" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E14" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N14" s="3">
         <v>300</v>
       </c>
       <c r="O14" s="3"/>
       <c r="P14" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Q14" s="3">
         <v>1</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T14" s="3"/>
       <c r="U14" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="4"/>
-      <c r="AA14" s="4"/>
+      <c r="X14" s="4"/>
+      <c r="Y14" s="4"/>
+      <c r="Z14" s="3"/>
+      <c r="AA14" s="3"/>
       <c r="AB14" s="3"/>
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
@@ -1949,58 +1944,58 @@
       <c r="AM14" s="3"/>
       <c r="AN14" s="3"/>
     </row>
-    <row r="15" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N15" s="3">
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="O15" s="3"/>
       <c r="P15" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Q15" s="3">
         <v>1</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T15" s="3"/>
       <c r="U15" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="4"/>
-      <c r="AA15" s="4"/>
+      <c r="X15" s="4"/>
+      <c r="Y15" s="4"/>
+      <c r="Z15" s="3"/>
+      <c r="AA15" s="3"/>
       <c r="AB15" s="3"/>
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
@@ -2015,58 +2010,58 @@
       <c r="AM15" s="3"/>
       <c r="AN15" s="3"/>
     </row>
-    <row r="16" spans="1:53" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N16" s="3">
         <v>1000</v>
       </c>
       <c r="O16" s="3"/>
       <c r="P16" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Q16" s="3">
         <v>1</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
-      <c r="Z16" s="4"/>
-      <c r="AA16" s="4"/>
+      <c r="X16" s="4"/>
+      <c r="Y16" s="4"/>
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
@@ -2081,58 +2076,58 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
     </row>
-    <row r="17" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N17" s="3">
         <v>5</v>
       </c>
       <c r="O17" s="3"/>
       <c r="P17" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Q17" s="3">
         <v>1</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T17" s="3"/>
       <c r="U17" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
-      <c r="Y17" s="3"/>
-      <c r="Z17" s="4"/>
-      <c r="AA17" s="4"/>
+      <c r="X17" s="4"/>
+      <c r="Y17" s="4"/>
+      <c r="Z17" s="3"/>
+      <c r="AA17" s="3"/>
       <c r="AB17" s="3"/>
       <c r="AC17" s="3"/>
       <c r="AD17" s="3"/>
@@ -2147,58 +2142,58 @@
       <c r="AM17" s="3"/>
       <c r="AN17" s="3"/>
     </row>
-    <row r="18" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N18" s="3">
         <v>1300</v>
       </c>
       <c r="O18" s="3"/>
       <c r="P18" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Q18" s="3">
         <v>1</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T18" s="3"/>
       <c r="U18" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="4"/>
-      <c r="AA18" s="4"/>
+      <c r="X18" s="4"/>
+      <c r="Y18" s="4"/>
+      <c r="Z18" s="3"/>
+      <c r="AA18" s="3"/>
       <c r="AB18" s="3"/>
       <c r="AC18" s="3"/>
       <c r="AD18" s="3"/>
@@ -2213,58 +2208,58 @@
       <c r="AM18" s="3"/>
       <c r="AN18" s="3"/>
     </row>
-    <row r="19" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N19" s="3">
         <v>4000</v>
       </c>
       <c r="O19" s="3"/>
       <c r="P19" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Q19" s="3">
         <v>1</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T19" s="3"/>
       <c r="U19" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="4"/>
-      <c r="AA19" s="4"/>
+      <c r="X19" s="4"/>
+      <c r="Y19" s="4"/>
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
@@ -2279,58 +2274,58 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
     </row>
-    <row r="20" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N20" s="3">
         <v>300</v>
       </c>
       <c r="O20" s="3"/>
       <c r="P20" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Q20" s="3">
         <v>1</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T20" s="3"/>
       <c r="U20" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
-      <c r="X20" s="3"/>
-      <c r="Y20" s="3"/>
-      <c r="Z20" s="4"/>
-      <c r="AA20" s="4"/>
+      <c r="X20" s="4"/>
+      <c r="Y20" s="4"/>
+      <c r="Z20" s="3"/>
+      <c r="AA20" s="3"/>
       <c r="AB20" s="3"/>
       <c r="AC20" s="3"/>
       <c r="AD20" s="3"/>
@@ -2345,58 +2340,58 @@
       <c r="AM20" s="3"/>
       <c r="AN20" s="3"/>
     </row>
-    <row r="21" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N21" s="3">
         <v>15</v>
       </c>
       <c r="O21" s="3"/>
       <c r="P21" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Q21" s="3">
         <v>1</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T21" s="3"/>
       <c r="U21" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
-      <c r="X21" s="3"/>
-      <c r="Y21" s="3"/>
-      <c r="Z21" s="4"/>
-      <c r="AA21" s="4"/>
+      <c r="X21" s="4"/>
+      <c r="Y21" s="4"/>
+      <c r="Z21" s="3"/>
+      <c r="AA21" s="3"/>
       <c r="AB21" s="3"/>
       <c r="AC21" s="3"/>
       <c r="AD21" s="3"/>
@@ -2411,58 +2406,58 @@
       <c r="AM21" s="3"/>
       <c r="AN21" s="3"/>
     </row>
-    <row r="22" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N22" s="3">
         <v>610</v>
       </c>
       <c r="O22" s="3"/>
       <c r="P22" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Q22" s="3">
         <v>1</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T22" s="3"/>
       <c r="U22" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
-      <c r="X22" s="3"/>
-      <c r="Y22" s="3"/>
-      <c r="Z22" s="4"/>
-      <c r="AA22" s="4"/>
+      <c r="X22" s="4"/>
+      <c r="Y22" s="4"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
       <c r="AB22" s="3"/>
       <c r="AC22" s="3"/>
       <c r="AD22" s="3"/>
@@ -2477,58 +2472,58 @@
       <c r="AM22" s="3"/>
       <c r="AN22" s="3"/>
     </row>
-    <row r="23" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N23" s="3">
         <v>50</v>
       </c>
       <c r="O23" s="3"/>
       <c r="P23" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Q23" s="3">
         <v>1</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T23" s="3"/>
       <c r="U23" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
-      <c r="X23" s="3"/>
-      <c r="Y23" s="3"/>
-      <c r="Z23" s="4"/>
-      <c r="AA23" s="4"/>
+      <c r="X23" s="4"/>
+      <c r="Y23" s="4"/>
+      <c r="Z23" s="3"/>
+      <c r="AA23" s="3"/>
       <c r="AB23" s="3"/>
       <c r="AC23" s="3"/>
       <c r="AD23" s="3"/>
@@ -2543,60 +2538,60 @@
       <c r="AM23" s="3"/>
       <c r="AN23" s="3"/>
     </row>
-    <row r="24" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N24" s="3">
         <v>7400</v>
       </c>
       <c r="O24" s="3"/>
       <c r="P24" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Q24" s="3">
         <v>1</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T24" s="3">
         <v>1</v>
       </c>
       <c r="U24" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
-      <c r="X24" s="3"/>
-      <c r="Y24" s="3"/>
-      <c r="Z24" s="4"/>
-      <c r="AA24" s="4"/>
+      <c r="X24" s="4"/>
+      <c r="Y24" s="4"/>
+      <c r="Z24" s="3"/>
+      <c r="AA24" s="3"/>
       <c r="AB24" s="3"/>
       <c r="AC24" s="3"/>
       <c r="AD24" s="3"/>
@@ -2611,68 +2606,66 @@
       <c r="AM24" s="3"/>
       <c r="AN24" s="3"/>
     </row>
-    <row r="25" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N25" s="3">
         <v>235</v>
       </c>
       <c r="O25" s="3"/>
       <c r="P25" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="Q25" s="3">
         <v>1</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="T25" s="3">
         <v>1</v>
       </c>
       <c r="U25" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
-      <c r="Y25" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="Z25" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA25" s="4" t="s">
-        <v>126</v>
-      </c>
+      <c r="X25" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y25" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z25" s="3"/>
+      <c r="AA25" s="3"/>
       <c r="AB25" s="3"/>
       <c r="AC25" s="3"/>
       <c r="AD25" s="3"/>
@@ -2687,68 +2680,66 @@
       <c r="AM25" s="3"/>
       <c r="AN25" s="3"/>
     </row>
-    <row r="26" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E26" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N26" s="3">
         <v>235</v>
       </c>
       <c r="O26" s="3"/>
       <c r="P26" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="Q26" s="3">
         <v>1</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="T26" s="3">
         <v>1</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
-      <c r="X26" s="3"/>
-      <c r="Y26" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="Z26" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA26" s="4" t="s">
-        <v>126</v>
-      </c>
+      <c r="X26" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y26" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z26" s="3"/>
+      <c r="AA26" s="3"/>
       <c r="AB26" s="3"/>
       <c r="AC26" s="3"/>
       <c r="AD26" s="3"/>
@@ -2763,66 +2754,64 @@
       <c r="AM26" s="3"/>
       <c r="AN26" s="3"/>
     </row>
-    <row r="27" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N27" s="3">
         <v>126</v>
       </c>
       <c r="O27" s="3"/>
       <c r="P27" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="Q27" s="3">
         <v>1</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="T27" s="3">
         <v>1</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
-      <c r="X27" s="3"/>
-      <c r="Y27" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="Z27" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA27" s="4" t="s">
-        <v>126</v>
-      </c>
+      <c r="X27" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y27" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z27" s="3"/>
+      <c r="AA27" s="3"/>
       <c r="AB27" s="3"/>
       <c r="AC27" s="3"/>
       <c r="AD27" s="3"/>
@@ -2837,66 +2826,64 @@
       <c r="AM27" s="3"/>
       <c r="AN27" s="3"/>
     </row>
-    <row r="28" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E28" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N28" s="3">
         <v>126</v>
       </c>
       <c r="O28" s="3"/>
       <c r="P28" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="Q28" s="3">
         <v>1</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="T28" s="3">
         <v>1</v>
       </c>
       <c r="U28" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
-      <c r="X28" s="3"/>
-      <c r="Y28" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="Z28" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA28" s="4" t="s">
-        <v>126</v>
-      </c>
+      <c r="X28" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y28" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z28" s="3"/>
+      <c r="AA28" s="3"/>
       <c r="AB28" s="3"/>
       <c r="AC28" s="3"/>
       <c r="AD28" s="3"/>
@@ -2911,66 +2898,64 @@
       <c r="AM28" s="3"/>
       <c r="AN28" s="3"/>
     </row>
-    <row r="29" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N29" s="3">
         <v>126</v>
       </c>
       <c r="O29" s="3"/>
       <c r="P29" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="Q29" s="3">
         <v>1</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="T29" s="3">
         <v>1</v>
       </c>
       <c r="U29" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
-      <c r="X29" s="3"/>
-      <c r="Y29" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="Z29" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA29" s="4" t="s">
-        <v>126</v>
-      </c>
+      <c r="X29" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y29" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z29" s="3"/>
+      <c r="AA29" s="3"/>
       <c r="AB29" s="3"/>
       <c r="AC29" s="3"/>
       <c r="AD29" s="3"/>
@@ -2985,64 +2970,64 @@
       <c r="AM29" s="3"/>
       <c r="AN29" s="3"/>
     </row>
-    <row r="30" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E30" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N30" s="3">
         <v>6.5</v>
       </c>
       <c r="O30" s="3"/>
       <c r="P30" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q30" s="3">
         <v>30</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="T30" s="3">
         <v>1</v>
       </c>
       <c r="U30" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
-      <c r="X30" s="3"/>
-      <c r="Y30" s="3"/>
-      <c r="Z30" s="4"/>
-      <c r="AA30" s="4"/>
+      <c r="X30" s="4"/>
+      <c r="Y30" s="4"/>
+      <c r="Z30" s="3"/>
+      <c r="AA30" s="3"/>
       <c r="AB30" s="3"/>
       <c r="AC30" s="3"/>
       <c r="AD30" s="3"/>
@@ -3057,64 +3042,64 @@
       <c r="AM30" s="3"/>
       <c r="AN30" s="3"/>
     </row>
-    <row r="31" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E31" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N31" s="3">
         <v>5.5</v>
       </c>
       <c r="O31" s="3"/>
       <c r="P31" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q31" s="3">
         <v>30</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="T31" s="3">
         <v>1</v>
       </c>
       <c r="U31" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
-      <c r="X31" s="3"/>
-      <c r="Y31" s="3"/>
-      <c r="Z31" s="4"/>
-      <c r="AA31" s="4"/>
+      <c r="X31" s="4"/>
+      <c r="Y31" s="4"/>
+      <c r="Z31" s="3"/>
+      <c r="AA31" s="3"/>
       <c r="AB31" s="3"/>
       <c r="AC31" s="3"/>
       <c r="AD31" s="3"/>
@@ -3129,64 +3114,64 @@
       <c r="AM31" s="3"/>
       <c r="AN31" s="3"/>
     </row>
-    <row r="32" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E32" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N32" s="3">
         <v>9.5</v>
       </c>
       <c r="O32" s="3"/>
       <c r="P32" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q32" s="3">
         <v>7</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S32" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="T32" s="3">
         <v>1</v>
       </c>
       <c r="U32" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
-      <c r="X32" s="3"/>
-      <c r="Y32" s="3"/>
-      <c r="Z32" s="4"/>
-      <c r="AA32" s="4"/>
+      <c r="X32" s="4"/>
+      <c r="Y32" s="4"/>
+      <c r="Z32" s="3"/>
+      <c r="AA32" s="3"/>
       <c r="AB32" s="3"/>
       <c r="AC32" s="3"/>
       <c r="AD32" s="3"/>
@@ -3201,64 +3186,64 @@
       <c r="AM32" s="3"/>
       <c r="AN32" s="3"/>
     </row>
-    <row r="33" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E33" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N33" s="3">
         <v>6</v>
       </c>
       <c r="O33" s="3"/>
       <c r="P33" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q33" s="3">
         <v>7</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S33" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="T33" s="3">
         <v>1</v>
       </c>
       <c r="U33" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
-      <c r="X33" s="3"/>
-      <c r="Y33" s="3"/>
-      <c r="Z33" s="4"/>
-      <c r="AA33" s="4"/>
+      <c r="X33" s="4"/>
+      <c r="Y33" s="4"/>
+      <c r="Z33" s="3"/>
+      <c r="AA33" s="3"/>
       <c r="AB33" s="3"/>
       <c r="AC33" s="3"/>
       <c r="AD33" s="3"/>
@@ -3273,64 +3258,64 @@
       <c r="AM33" s="3"/>
       <c r="AN33" s="3"/>
     </row>
-    <row r="34" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E34" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N34" s="3">
         <v>8</v>
       </c>
       <c r="O34" s="3"/>
       <c r="P34" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q34" s="3">
         <v>1</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S34" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="T34" s="3">
         <v>1</v>
       </c>
       <c r="U34" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
-      <c r="X34" s="3"/>
-      <c r="Y34" s="3"/>
-      <c r="Z34" s="4"/>
-      <c r="AA34" s="4"/>
+      <c r="X34" s="4"/>
+      <c r="Y34" s="4"/>
+      <c r="Z34" s="3"/>
+      <c r="AA34" s="3"/>
       <c r="AB34" s="3"/>
       <c r="AC34" s="3"/>
       <c r="AD34" s="3"/>
@@ -3345,64 +3330,64 @@
       <c r="AM34" s="3"/>
       <c r="AN34" s="3"/>
     </row>
-    <row r="35" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E35" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N35" s="3">
         <v>4</v>
       </c>
       <c r="O35" s="3"/>
       <c r="P35" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q35" s="3">
         <v>1</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S35" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="T35" s="3">
         <v>1</v>
       </c>
       <c r="U35" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
-      <c r="X35" s="3"/>
-      <c r="Y35" s="3"/>
-      <c r="Z35" s="4"/>
-      <c r="AA35" s="4"/>
+      <c r="X35" s="4"/>
+      <c r="Y35" s="4"/>
+      <c r="Z35" s="3"/>
+      <c r="AA35" s="3"/>
       <c r="AB35" s="3"/>
       <c r="AC35" s="3"/>
       <c r="AD35" s="3"/>
@@ -3417,64 +3402,64 @@
       <c r="AM35" s="3"/>
       <c r="AN35" s="3"/>
     </row>
-    <row r="36" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E36" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N36" s="3">
         <v>5</v>
       </c>
       <c r="O36" s="3"/>
       <c r="P36" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q36" s="3">
         <v>1</v>
       </c>
       <c r="R36" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S36" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="T36" s="3">
         <v>1</v>
       </c>
       <c r="U36" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
-      <c r="X36" s="3"/>
-      <c r="Y36" s="3"/>
-      <c r="Z36" s="4"/>
-      <c r="AA36" s="4"/>
+      <c r="X36" s="4"/>
+      <c r="Y36" s="4"/>
+      <c r="Z36" s="3"/>
+      <c r="AA36" s="3"/>
       <c r="AB36" s="3"/>
       <c r="AC36" s="3"/>
       <c r="AD36" s="3"/>
@@ -3489,64 +3474,64 @@
       <c r="AM36" s="3"/>
       <c r="AN36" s="3"/>
     </row>
-    <row r="37" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E37" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N37" s="3">
         <v>3</v>
       </c>
       <c r="O37" s="3"/>
       <c r="P37" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q37" s="3">
         <v>1</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="T37" s="3">
         <v>1</v>
       </c>
       <c r="U37" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
-      <c r="X37" s="3"/>
-      <c r="Y37" s="3"/>
-      <c r="Z37" s="4"/>
-      <c r="AA37" s="4"/>
+      <c r="X37" s="4"/>
+      <c r="Y37" s="4"/>
+      <c r="Z37" s="3"/>
+      <c r="AA37" s="3"/>
       <c r="AB37" s="3"/>
       <c r="AC37" s="3"/>
       <c r="AD37" s="3"/>
@@ -3561,64 +3546,64 @@
       <c r="AM37" s="3"/>
       <c r="AN37" s="3"/>
     </row>
-    <row r="38" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E38" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N38" s="3">
         <v>5</v>
       </c>
       <c r="O38" s="3"/>
       <c r="P38" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q38" s="3">
         <v>7</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="T38" s="3">
         <v>1</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
-      <c r="X38" s="3"/>
-      <c r="Y38" s="3"/>
-      <c r="Z38" s="4"/>
-      <c r="AA38" s="4"/>
+      <c r="X38" s="4"/>
+      <c r="Y38" s="4"/>
+      <c r="Z38" s="3"/>
+      <c r="AA38" s="3"/>
       <c r="AB38" s="3"/>
       <c r="AC38" s="3"/>
       <c r="AD38" s="3"/>
@@ -3633,64 +3618,64 @@
       <c r="AM38" s="3"/>
       <c r="AN38" s="3"/>
     </row>
-    <row r="39" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E39" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N39" s="3">
         <v>4</v>
       </c>
       <c r="O39" s="3"/>
       <c r="P39" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q39" s="3">
         <v>7</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="T39" s="3">
         <v>1</v>
       </c>
       <c r="U39" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-      <c r="X39" s="3"/>
-      <c r="Y39" s="3"/>
-      <c r="Z39" s="4"/>
-      <c r="AA39" s="4"/>
+      <c r="X39" s="4"/>
+      <c r="Y39" s="4"/>
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
@@ -3705,70 +3690,70 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
     </row>
-    <row r="40" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E40" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q40" s="3">
         <v>1</v>
       </c>
       <c r="R40" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S40" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T40" s="3">
         <v>1</v>
       </c>
       <c r="U40" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-      <c r="X40" s="3"/>
-      <c r="Y40" s="3"/>
-      <c r="Z40" s="4"/>
-      <c r="AA40" s="4"/>
+      <c r="X40" s="4"/>
+      <c r="Y40" s="4"/>
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AF40" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
@@ -3784,70 +3769,70 @@
       </c>
       <c r="AN40" s="3"/>
     </row>
-    <row r="41" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E41" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N41" s="3"/>
       <c r="O41" s="3"/>
       <c r="P41" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q41" s="3">
         <v>30</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S41" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="T41" s="3">
         <v>1</v>
       </c>
       <c r="U41" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
-      <c r="X41" s="3"/>
-      <c r="Y41" s="3"/>
-      <c r="Z41" s="4"/>
-      <c r="AA41" s="4"/>
+      <c r="X41" s="4"/>
+      <c r="Y41" s="4"/>
+      <c r="Z41" s="3"/>
+      <c r="AA41" s="3"/>
       <c r="AB41" s="3"/>
       <c r="AC41" s="3"/>
       <c r="AD41" s="3"/>
       <c r="AE41" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AF41" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AG41" s="3"/>
       <c r="AH41" s="3"/>
@@ -3863,70 +3848,70 @@
       </c>
       <c r="AN41" s="3"/>
     </row>
-    <row r="42" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E42" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N42" s="3"/>
       <c r="O42" s="3"/>
       <c r="P42" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q42" s="3">
         <v>1</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S42" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T42" s="3">
         <v>1</v>
       </c>
       <c r="U42" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
-      <c r="X42" s="3"/>
-      <c r="Y42" s="3"/>
-      <c r="Z42" s="4"/>
-      <c r="AA42" s="4"/>
+      <c r="X42" s="4"/>
+      <c r="Y42" s="4"/>
+      <c r="Z42" s="3"/>
+      <c r="AA42" s="3"/>
       <c r="AB42" s="3"/>
       <c r="AC42" s="3"/>
       <c r="AD42" s="3"/>
       <c r="AE42" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AF42" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG42" s="3"/>
       <c r="AH42" s="3"/>
@@ -3942,70 +3927,70 @@
       </c>
       <c r="AN42" s="3"/>
     </row>
-    <row r="43" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E43" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N43" s="3"/>
       <c r="O43" s="3"/>
       <c r="P43" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q43" s="3">
         <v>30</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S43" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="T43" s="3">
         <v>1</v>
       </c>
       <c r="U43" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3"/>
-      <c r="X43" s="3"/>
-      <c r="Y43" s="3"/>
-      <c r="Z43" s="4"/>
-      <c r="AA43" s="4"/>
+      <c r="X43" s="4"/>
+      <c r="Y43" s="4"/>
+      <c r="Z43" s="3"/>
+      <c r="AA43" s="3"/>
       <c r="AB43" s="3"/>
       <c r="AC43" s="3"/>
       <c r="AD43" s="3"/>
       <c r="AE43" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AF43" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG43" s="3"/>
       <c r="AH43" s="3"/>
@@ -4021,70 +4006,70 @@
       </c>
       <c r="AN43" s="3"/>
     </row>
-    <row r="44" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E44" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G44" s="3"/>
       <c r="H44" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I44" s="3"/>
       <c r="J44" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N44" s="3"/>
       <c r="O44" s="3"/>
       <c r="P44" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q44" s="3">
         <v>1</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S44" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T44" s="3">
         <v>1</v>
       </c>
       <c r="U44" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
-      <c r="X44" s="3"/>
-      <c r="Y44" s="3"/>
-      <c r="Z44" s="4"/>
-      <c r="AA44" s="4"/>
+      <c r="X44" s="4"/>
+      <c r="Y44" s="4"/>
+      <c r="Z44" s="3"/>
+      <c r="AA44" s="3"/>
       <c r="AB44" s="3"/>
       <c r="AC44" s="3"/>
       <c r="AD44" s="3"/>
       <c r="AE44" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AF44" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AG44" s="3"/>
       <c r="AH44" s="3"/>
@@ -4100,70 +4085,70 @@
       </c>
       <c r="AN44" s="3"/>
     </row>
-    <row r="45" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E45" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
       <c r="P45" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q45" s="3">
         <v>30</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S45" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="T45" s="3">
         <v>1</v>
       </c>
       <c r="U45" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V45" s="3"/>
       <c r="W45" s="3"/>
-      <c r="X45" s="3"/>
-      <c r="Y45" s="3"/>
-      <c r="Z45" s="4"/>
-      <c r="AA45" s="4"/>
+      <c r="X45" s="4"/>
+      <c r="Y45" s="4"/>
+      <c r="Z45" s="3"/>
+      <c r="AA45" s="3"/>
       <c r="AB45" s="3"/>
       <c r="AC45" s="3"/>
       <c r="AD45" s="3"/>
       <c r="AE45" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AF45" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AG45" s="3"/>
       <c r="AH45" s="3"/>
@@ -4179,70 +4164,70 @@
       </c>
       <c r="AN45" s="3"/>
     </row>
-    <row r="46" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E46" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
       <c r="P46" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q46" s="3">
         <v>1</v>
       </c>
       <c r="R46" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S46" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T46" s="3">
         <v>1</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
-      <c r="X46" s="3"/>
-      <c r="Y46" s="3"/>
-      <c r="Z46" s="4"/>
-      <c r="AA46" s="4"/>
+      <c r="X46" s="4"/>
+      <c r="Y46" s="4"/>
+      <c r="Z46" s="3"/>
+      <c r="AA46" s="3"/>
       <c r="AB46" s="3"/>
       <c r="AC46" s="3"/>
       <c r="AD46" s="3"/>
       <c r="AE46" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AF46" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AG46" s="3"/>
       <c r="AH46" s="3"/>
@@ -4258,70 +4243,70 @@
       </c>
       <c r="AN46" s="3"/>
     </row>
-    <row r="47" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E47" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
       <c r="P47" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q47" s="3">
         <v>30</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S47" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="T47" s="3">
         <v>1</v>
       </c>
       <c r="U47" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
-      <c r="X47" s="3"/>
-      <c r="Y47" s="3"/>
-      <c r="Z47" s="4"/>
-      <c r="AA47" s="4"/>
+      <c r="X47" s="4"/>
+      <c r="Y47" s="4"/>
+      <c r="Z47" s="3"/>
+      <c r="AA47" s="3"/>
       <c r="AB47" s="3"/>
       <c r="AC47" s="3"/>
       <c r="AD47" s="3"/>
       <c r="AE47" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AF47" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AG47" s="3"/>
       <c r="AH47" s="3"/>
@@ -4337,70 +4322,70 @@
       </c>
       <c r="AN47" s="3"/>
     </row>
-    <row r="48" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E48" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I48" s="3"/>
       <c r="J48" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
       <c r="P48" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q48" s="3">
         <v>1</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T48" s="3">
         <v>1</v>
       </c>
       <c r="U48" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
-      <c r="X48" s="3"/>
-      <c r="Y48" s="3"/>
-      <c r="Z48" s="4"/>
-      <c r="AA48" s="4"/>
+      <c r="X48" s="4"/>
+      <c r="Y48" s="4"/>
+      <c r="Z48" s="3"/>
+      <c r="AA48" s="3"/>
       <c r="AB48" s="3"/>
       <c r="AC48" s="3"/>
       <c r="AD48" s="3"/>
       <c r="AE48" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AF48" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AG48" s="3"/>
       <c r="AH48" s="3"/>
@@ -4416,70 +4401,70 @@
       </c>
       <c r="AN48" s="3"/>
     </row>
-    <row r="49" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E49" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I49" s="3"/>
       <c r="J49" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N49" s="3"/>
       <c r="O49" s="3"/>
       <c r="P49" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q49" s="3">
         <v>1</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S49" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T49" s="3">
         <v>1</v>
       </c>
       <c r="U49" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="3"/>
-      <c r="X49" s="3"/>
-      <c r="Y49" s="3"/>
-      <c r="Z49" s="4"/>
-      <c r="AA49" s="4"/>
+      <c r="X49" s="4"/>
+      <c r="Y49" s="4"/>
+      <c r="Z49" s="3"/>
+      <c r="AA49" s="3"/>
       <c r="AB49" s="3"/>
       <c r="AC49" s="3"/>
       <c r="AD49" s="3"/>
       <c r="AE49" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AF49" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="AG49" s="3"/>
       <c r="AH49" s="3"/>
@@ -4495,70 +4480,70 @@
       </c>
       <c r="AN49" s="3"/>
     </row>
-    <row r="50" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="E50" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I50" s="3"/>
       <c r="J50" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="3"/>
       <c r="P50" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q50" s="3">
         <v>30</v>
       </c>
       <c r="R50" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S50" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="T50" s="3">
         <v>1</v>
       </c>
       <c r="U50" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
-      <c r="X50" s="3"/>
-      <c r="Y50" s="3"/>
-      <c r="Z50" s="4"/>
-      <c r="AA50" s="4"/>
+      <c r="X50" s="4"/>
+      <c r="Y50" s="4"/>
+      <c r="Z50" s="3"/>
+      <c r="AA50" s="3"/>
       <c r="AB50" s="3"/>
       <c r="AC50" s="3"/>
       <c r="AD50" s="3"/>
       <c r="AE50" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AF50" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="AG50" s="3"/>
       <c r="AH50" s="3"/>
